--- a/data/govspending.xlsx
+++ b/data/govspending.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7812" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7812"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Сезонно скорректированные" sheetId="3" r:id="rId3"/>
+    <sheet name="Сезонно скорректированные2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
   <si>
     <t>Федеральный бюджет</t>
   </si>
@@ -51,21 +52,6 @@
   </si>
   <si>
     <t>Единица измерения: руб.</t>
-  </si>
-  <si>
-    <t>33 881 799 545 304,10</t>
-  </si>
-  <si>
-    <t>21 859 811 479 300,00</t>
-  </si>
-  <si>
-    <t>17 586 741 067 765,58</t>
-  </si>
-  <si>
-    <t>28 835 482 914 038,65</t>
-  </si>
-  <si>
-    <t>20 735 401 409 952,56</t>
   </si>
   <si>
     <t>Прирост исполненного</t>
@@ -820,7 +806,7 @@
     <xf numFmtId="43" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="42" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -840,10 +826,12 @@
     <xf numFmtId="3" fontId="43" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="69" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="44" fillId="0" borderId="0" xfId="69" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="45" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -856,9 +844,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="70">
@@ -1209,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
@@ -1248,10 +1233,10 @@
     </row>
     <row r="2" spans="1:13" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
@@ -1288,11 +1273,11 @@
       <c r="A3" s="1">
         <v>41640</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>C3/D3</f>
         <v>4.455966420199349E-2</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <f>E3</f>
         <v>1452808895239.28</v>
       </c>
@@ -1333,11 +1318,11 @@
       <c r="A4" s="1">
         <v>41671</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f t="shared" ref="B4:B67" si="0">C4/D4</f>
         <v>8.7318170049497726E-2</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <f>E4-E3</f>
         <v>2855916288926.6201</v>
       </c>
@@ -1378,11 +1363,11 @@
       <c r="A5" s="1">
         <v>41699</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <f t="shared" si="0"/>
         <v>7.5680716935203618E-2</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <f t="shared" ref="C5:C14" si="3">E5-E4</f>
         <v>2493370755431.5903</v>
       </c>
@@ -1423,11 +1408,11 @@
       <c r="A6" s="1">
         <v>41730</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <f t="shared" si="0"/>
         <v>8.7840193045120599E-2</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <f t="shared" si="3"/>
         <v>2924844680409.8613</v>
       </c>
@@ -1468,11 +1453,11 @@
       <c r="A7" s="1">
         <v>41760</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f t="shared" si="0"/>
         <v>6.4943332025611464E-2</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <f t="shared" si="3"/>
         <v>2174666553888.6797</v>
       </c>
@@ -1513,11 +1498,11 @@
       <c r="A8" s="1">
         <v>41791</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f t="shared" si="0"/>
         <v>7.486436229124413E-2</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f t="shared" si="3"/>
         <v>2516168151501.3691</v>
       </c>
@@ -1558,11 +1543,11 @@
       <c r="A9" s="1">
         <v>41821</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <f t="shared" si="0"/>
         <v>7.9109253097964835E-2</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f t="shared" si="3"/>
         <v>2667163008233.5605</v>
       </c>
@@ -1603,11 +1588,11 @@
       <c r="A10" s="1">
         <v>41852</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <f t="shared" si="0"/>
         <v>7.0990945372778919E-2</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <f t="shared" si="3"/>
         <v>2398723873756.4297</v>
       </c>
@@ -1648,11 +1633,11 @@
       <c r="A11" s="1">
         <v>41883</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>7.5191642969707859E-2</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f t="shared" si="3"/>
         <v>2547722724138.7734</v>
       </c>
@@ -1693,11 +1678,11 @@
       <c r="A12" s="1">
         <v>41913</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>8.5505353459643052E-2</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f t="shared" si="3"/>
         <v>2901961405430.7656</v>
       </c>
@@ -1738,11 +1723,11 @@
       <c r="A13" s="1">
         <v>41944</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>7.015055606896374E-2</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f t="shared" si="3"/>
         <v>2383569938670.1484</v>
       </c>
@@ -1783,11 +1768,11 @@
       <c r="A14" s="1">
         <v>41974</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f t="shared" si="0"/>
         <v>0.16937139917747276</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f t="shared" si="3"/>
         <v>5932401498120.543</v>
       </c>
@@ -1828,11 +1813,11 @@
       <c r="A15" s="1">
         <v>42005</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <f t="shared" si="0"/>
         <v>6.7308481627115085E-2</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f>E15</f>
         <v>2447081435343.3701</v>
       </c>
@@ -1873,11 +1858,11 @@
       <c r="A16" s="1">
         <v>42036</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f t="shared" si="0"/>
         <v>7.9218046152364899E-2</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f>E16-E15</f>
         <v>2885909717401.5098</v>
       </c>
@@ -1918,11 +1903,11 @@
       <c r="A17" s="1">
         <v>42064</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <f t="shared" si="0"/>
         <v>7.569905212068502E-2</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <f t="shared" ref="C17:C26" si="4">E17-E16</f>
         <v>2779488709348.9297</v>
       </c>
@@ -1963,11 +1948,11 @@
       <c r="A18" s="1">
         <v>42095</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <f t="shared" si="0"/>
         <v>9.9435929331961576E-2</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <f t="shared" si="4"/>
         <v>3633684010619.7197</v>
       </c>
@@ -2008,11 +1993,11 @@
       <c r="A19" s="1">
         <v>42125</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <f t="shared" si="0"/>
         <v>6.3413259412510664E-2</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <f t="shared" si="4"/>
         <v>2334857093067.6309</v>
       </c>
@@ -2053,11 +2038,11 @@
       <c r="A20" s="1">
         <v>42156</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <f t="shared" si="0"/>
         <v>7.6707905535151888E-2</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <f t="shared" si="4"/>
         <v>2834589813444.4609</v>
       </c>
@@ -2098,11 +2083,11 @@
       <c r="A21" s="1">
         <v>42186</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <f t="shared" si="0"/>
         <v>8.4243417369598644E-2</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <f t="shared" si="4"/>
         <v>3120073809589.5781</v>
       </c>
@@ -2143,11 +2128,11 @@
       <c r="A22" s="1">
         <v>42217</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <f t="shared" si="0"/>
         <v>7.0458064891046238E-2</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <f t="shared" si="4"/>
         <v>2613769491650.875</v>
       </c>
@@ -2188,11 +2173,11 @@
       <c r="A23" s="1">
         <v>42248</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <f t="shared" si="0"/>
         <v>6.87075732368677E-2</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <f t="shared" si="4"/>
         <v>2553986032160.3164</v>
       </c>
@@ -2233,11 +2218,11 @@
       <c r="A24" s="1">
         <v>42278</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <f t="shared" si="0"/>
         <v>7.5784362901564956E-2</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <f t="shared" si="4"/>
         <v>2824039575607.293</v>
       </c>
@@ -2278,11 +2263,11 @@
       <c r="A25" s="1">
         <v>42309</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <f t="shared" si="0"/>
         <v>7.0834342921987994E-2</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <f t="shared" si="4"/>
         <v>2661255834701.2148</v>
       </c>
@@ -2323,11 +2308,11 @@
       <c r="A26" s="1">
         <v>42339</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <f t="shared" si="0"/>
         <v>0.14542702922387979</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <f t="shared" si="4"/>
         <v>5494857451528.3437</v>
       </c>
@@ -2368,11 +2353,11 @@
       <c r="A27" s="1">
         <v>42370</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <f t="shared" si="0"/>
         <v>4.5102894272130517E-2</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <f>E27</f>
         <v>1674872672706.8899</v>
       </c>
@@ -2413,11 +2398,11 @@
       <c r="A28" s="1">
         <v>42401</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <f t="shared" si="0"/>
         <v>7.5476699104046918E-2</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <f>E28-E27</f>
         <v>2810642618042.7402</v>
       </c>
@@ -2458,11 +2443,11 @@
       <c r="A29" s="1">
         <v>42430</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <f t="shared" si="0"/>
         <v>9.4514353441502205E-2</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <f t="shared" ref="C29:C38" si="5">E29-E28</f>
         <v>3541161805021.5889</v>
       </c>
@@ -2503,11 +2488,11 @@
       <c r="A30" s="1">
         <v>42461</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <f t="shared" si="0"/>
         <v>8.9249124192946755E-2</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <f t="shared" si="5"/>
         <v>3363111052687.5605</v>
       </c>
@@ -2548,11 +2533,11 @@
       <c r="A31" s="1">
         <v>42491</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <f t="shared" si="0"/>
         <v>6.8815823620138078E-2</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <f t="shared" si="5"/>
         <v>2608444530970.3008</v>
       </c>
@@ -2593,11 +2578,11 @@
       <c r="A32" s="1">
         <v>42522</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <f t="shared" si="0"/>
         <v>7.9644534649893281E-2</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="10">
         <f t="shared" si="5"/>
         <v>3034426495565.5078</v>
       </c>
@@ -2638,11 +2623,11 @@
       <c r="A33" s="1">
         <v>42552</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <f t="shared" si="0"/>
         <v>7.2922086652311521E-2</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <f t="shared" si="5"/>
         <v>2786218866898.502</v>
       </c>
@@ -2683,11 +2668,11 @@
       <c r="A34" s="1">
         <v>42583</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <f t="shared" si="0"/>
         <v>7.5233423631754406E-2</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <f t="shared" si="5"/>
         <v>2887938189341.082</v>
       </c>
@@ -2728,11 +2713,11 @@
       <c r="A35" s="1">
         <v>42614</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <f t="shared" si="0"/>
         <v>7.6221359983037792E-2</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <f t="shared" si="5"/>
         <v>2932328694406.2461</v>
       </c>
@@ -2773,11 +2758,11 @@
       <c r="A36" s="1">
         <v>42644</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <f t="shared" si="0"/>
         <v>7.4471984938858871E-2</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <f t="shared" si="5"/>
         <v>2870491510236.1328</v>
       </c>
@@ -2818,11 +2803,11 @@
       <c r="A37" s="1">
         <v>42675</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <f t="shared" si="0"/>
         <v>7.7474411879997124E-2</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <f t="shared" si="5"/>
         <v>3020797872971.9687</v>
       </c>
@@ -2863,11 +2848,11 @@
       <c r="A38" s="1">
         <v>42705</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <f t="shared" si="0"/>
         <v>0.15641049509014004</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <f t="shared" si="5"/>
         <v>6097625439857.3945</v>
       </c>
@@ -2908,11 +2893,11 @@
       <c r="A39" s="1">
         <v>42736</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <f t="shared" si="0"/>
         <v>6.5213786491388634E-2</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <f>E39</f>
         <v>2548036804399.2803</v>
       </c>
@@ -2953,11 +2938,11 @@
       <c r="A40" s="1">
         <v>42767</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <f t="shared" si="0"/>
         <v>7.0010286595203627E-2</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <f>E40-E39</f>
         <v>2758284210988.2803</v>
       </c>
@@ -2998,11 +2983,11 @@
       <c r="A41" s="1">
         <v>42795</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <f t="shared" si="0"/>
         <v>8.7740425904915376E-2</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <f t="shared" ref="C41:C50" si="6">E41-E40</f>
         <v>3488515388403.8887</v>
       </c>
@@ -3043,11 +3028,11 @@
       <c r="A42" s="1">
         <v>42826</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <f t="shared" si="0"/>
         <v>8.0831877976049862E-2</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <f t="shared" si="6"/>
         <v>3229251332713.5605</v>
       </c>
@@ -3088,11 +3073,11 @@
       <c r="A43" s="1">
         <v>42856</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <f t="shared" si="0"/>
         <v>7.140272906247902E-2</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <f t="shared" si="6"/>
         <v>2862990975834.5</v>
       </c>
@@ -3133,11 +3118,11 @@
       <c r="A44" s="1">
         <v>42887</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <f t="shared" si="0"/>
         <v>7.7591925180026278E-2</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <f t="shared" si="6"/>
         <v>3123182914928.0605</v>
       </c>
@@ -3178,11 +3163,11 @@
       <c r="A45" s="1">
         <v>42917</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <f t="shared" si="0"/>
         <v>7.319335854030623E-2</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <f t="shared" si="6"/>
         <v>2981049809794.4102</v>
       </c>
@@ -3223,11 +3208,11 @@
       <c r="A46" s="1">
         <v>42948</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <f t="shared" si="0"/>
         <v>7.3283719354462915E-2</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <f t="shared" si="6"/>
         <v>2986417566961.2695</v>
       </c>
@@ -3268,11 +3253,11 @@
       <c r="A47" s="1">
         <v>42979</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <f t="shared" si="0"/>
         <v>7.4234531073113827E-2</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <f t="shared" si="6"/>
         <v>3028227531439.207</v>
       </c>
@@ -3313,11 +3298,11 @@
       <c r="A48" s="1">
         <v>43009</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <f t="shared" si="0"/>
         <v>7.7241316547473807E-2</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <f t="shared" si="6"/>
         <v>3166479398422.168</v>
       </c>
@@ -3358,11 +3343,11 @@
       <c r="A49" s="1">
         <v>43040</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <f t="shared" si="0"/>
         <v>7.9594415245820963E-2</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <f t="shared" si="6"/>
         <v>3276367817656.8203</v>
       </c>
@@ -3403,11 +3388,11 @@
       <c r="A50" s="1">
         <v>43070</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <f t="shared" si="0"/>
         <v>0.13978617922590339</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <f t="shared" si="6"/>
         <v>5756568839572.25</v>
       </c>
@@ -3448,11 +3433,11 @@
       <c r="A51" s="1">
         <v>43101</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <f t="shared" si="0"/>
         <v>5.6407514622649244E-2</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <f>E51</f>
         <v>2330374601127.5801</v>
       </c>
@@ -3493,11 +3478,11 @@
       <c r="A52" s="1">
         <v>43132</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <f t="shared" si="0"/>
         <v>7.0195115779144182E-2</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <f>E52-E51</f>
         <v>2926830443249.2598</v>
       </c>
@@ -3538,11 +3523,11 @@
       <c r="A53" s="1">
         <v>43160</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <f t="shared" si="0"/>
         <v>8.3449873953928236E-2</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <f t="shared" ref="C53:C62" si="7">E53-E52</f>
         <v>3499180452026.4609</v>
       </c>
@@ -3583,11 +3568,11 @@
       <c r="A54" s="1">
         <v>43191</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <f t="shared" si="0"/>
         <v>8.6163229955786333E-2</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <f t="shared" si="7"/>
         <v>3628156461152.5996</v>
       </c>
@@ -3628,11 +3613,11 @@
       <c r="A55" s="1">
         <v>43221</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <f t="shared" si="0"/>
         <v>7.1745398493539239E-2</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <f t="shared" si="7"/>
         <v>3035122679626.9883</v>
       </c>
@@ -3673,11 +3658,11 @@
       <c r="A56" s="1">
         <v>43252</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <f t="shared" si="0"/>
         <v>7.9304241856382088E-2</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <f t="shared" si="7"/>
         <v>3364158715441.0957</v>
       </c>
@@ -3718,11 +3703,11 @@
       <c r="A57" s="1">
         <v>43282</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <f t="shared" si="0"/>
         <v>7.8605261869730797E-2</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <f t="shared" si="7"/>
         <v>3353295043642.2031</v>
       </c>
@@ -3763,11 +3748,11 @@
       <c r="A58" s="1">
         <v>43313</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <f t="shared" si="0"/>
         <v>7.2354333512687094E-2</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <f t="shared" si="7"/>
         <v>3088841839205.8711</v>
       </c>
@@ -3808,11 +3793,11 @@
       <c r="A59" s="1">
         <v>43344</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <f t="shared" si="0"/>
         <v>7.1394362151297311E-2</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <f t="shared" si="7"/>
         <v>3053541107357.4531</v>
       </c>
@@ -3853,11 +3838,11 @@
       <c r="A60" s="1">
         <v>43374</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <f t="shared" si="0"/>
         <v>7.9153121714094568E-2</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="10">
         <f t="shared" si="7"/>
         <v>3396853509510.7773</v>
       </c>
@@ -3898,11 +3883,11 @@
       <c r="A61" s="1">
         <v>43405</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <f t="shared" si="0"/>
         <v>7.8046236354924359E-2</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <f t="shared" si="7"/>
         <v>3373280446982.9023</v>
       </c>
@@ -3943,11 +3928,11 @@
       <c r="A62" s="1">
         <v>43435</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="9">
         <f t="shared" si="0"/>
         <v>0.14617618648683828</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="10">
         <f t="shared" si="7"/>
         <v>6325973719213.9492</v>
       </c>
@@ -3988,11 +3973,11 @@
       <c r="A63" s="1">
         <v>43466</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <f t="shared" si="0"/>
         <v>5.3976626427885019E-2</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <f>E63</f>
         <v>2424221190875.9199</v>
       </c>
@@ -4033,11 +4018,11 @@
       <c r="A64" s="1">
         <v>43497</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="9">
         <f t="shared" si="0"/>
         <v>7.2400490429240169E-2</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <f>E64-E63</f>
         <v>3289467666248.4199</v>
       </c>
@@ -4078,11 +4063,11 @@
       <c r="A65" s="1">
         <v>43525</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <f t="shared" si="0"/>
         <v>7.6546318627117887E-2</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <f t="shared" ref="C65:C74" si="8">E65-E64</f>
         <v>3526864330788.8711</v>
       </c>
@@ -4123,11 +4108,11 @@
       <c r="A66" s="1">
         <v>43556</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <f t="shared" si="0"/>
         <v>8.767150958502469E-2</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="10">
         <f t="shared" si="8"/>
         <v>4056743029774.25</v>
       </c>
@@ -4168,11 +4153,11 @@
       <c r="A67" s="1">
         <v>43586</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <f t="shared" si="0"/>
         <v>6.2355825719220055E-2</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <f t="shared" si="8"/>
         <v>2894679737982.8887</v>
       </c>
@@ -4213,11 +4198,11 @@
       <c r="A68" s="1">
         <v>43617</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <f t="shared" ref="B68:B131" si="9">C68/D68</f>
         <v>7.476900908643469E-2</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <f t="shared" si="8"/>
         <v>3478627064916.5137</v>
       </c>
@@ -4258,11 +4243,11 @@
       <c r="A69" s="1">
         <v>43647</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <f t="shared" si="9"/>
         <v>7.9193454948139633E-2</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <f t="shared" si="8"/>
         <v>3720981322215.5937</v>
       </c>
@@ -4303,11 +4288,11 @@
       <c r="A70" s="1">
         <v>43678</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="9">
         <f t="shared" si="9"/>
         <v>7.1450607781841216E-2</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="10">
         <f t="shared" si="8"/>
         <v>3360651815314.5898</v>
       </c>
@@ -4348,11 +4333,11 @@
       <c r="A71" s="1">
         <v>43709</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="9">
         <f t="shared" si="9"/>
         <v>7.8265885346615646E-2</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <f t="shared" si="8"/>
         <v>3689489117938.4648</v>
       </c>
@@ -4393,11 +4378,11 @@
       <c r="A72" s="1">
         <v>43739</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="9">
         <f t="shared" si="9"/>
         <v>8.0963255749509924E-2</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="10">
         <f t="shared" si="8"/>
         <v>3828950163256.6016</v>
       </c>
@@ -4438,11 +4423,11 @@
       <c r="A73" s="1">
         <v>43770</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="9">
         <f t="shared" si="9"/>
         <v>7.8367729197036357E-2</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <f t="shared" si="8"/>
         <v>3712846679281.5195</v>
       </c>
@@ -4483,11 +4468,11 @@
       <c r="A74" s="1">
         <v>43800</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="9">
         <f t="shared" si="9"/>
         <v>0.15211768193004896</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <f t="shared" si="8"/>
         <v>7244071323321.6172</v>
       </c>
@@ -4528,11 +4513,11 @@
       <c r="A75" s="1">
         <v>43831</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <f t="shared" si="9"/>
         <v>6.226341166202172E-2</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <f>E75</f>
         <v>3081755006343.2695</v>
       </c>
@@ -4573,11 +4558,11 @@
       <c r="A76" s="1">
         <v>43862</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <f t="shared" si="9"/>
         <v>6.9662425802943961E-2</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <f>E76-E75</f>
         <v>3481045383272.9199</v>
       </c>
@@ -4618,11 +4603,11 @@
       <c r="A77" s="1">
         <v>43891</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <f t="shared" si="9"/>
         <v>8.4101128889670224E-2</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <f t="shared" ref="C77:C86" si="12">E77-E76</f>
         <v>4284046296964.832</v>
       </c>
@@ -4663,11 +4648,11 @@
       <c r="A78" s="1">
         <v>43922</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="9">
         <f t="shared" si="9"/>
         <v>9.1361743168674403E-2</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="10">
         <f t="shared" si="12"/>
         <v>4785979411202.0508</v>
       </c>
@@ -4708,11 +4693,11 @@
       <c r="A79" s="1">
         <v>43952</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="9">
         <f t="shared" si="9"/>
         <v>6.5239645228519369E-2</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <f t="shared" si="12"/>
         <v>3447076441944.166</v>
       </c>
@@ -4753,11 +4738,11 @@
       <c r="A80" s="1">
         <v>43983</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="9">
         <f t="shared" si="9"/>
         <v>8.9554766170601693E-2</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="10">
         <f t="shared" si="12"/>
         <v>4768676690284.7227</v>
       </c>
@@ -4798,11 +4783,11 @@
       <c r="A81" s="1">
         <v>44013</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="9">
         <f t="shared" si="9"/>
         <v>8.332830643090218E-2</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <f t="shared" si="12"/>
         <v>4451483705756.3086</v>
       </c>
@@ -4843,11 +4828,11 @@
       <c r="A82" s="1">
         <v>44044</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="9">
         <f t="shared" si="9"/>
         <v>6.8631240956743403E-2</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="10">
         <f t="shared" si="12"/>
         <v>3800678732572.0586</v>
       </c>
@@ -4888,11 +4873,11 @@
       <c r="A83" s="1">
         <v>44075</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="9">
         <f t="shared" si="9"/>
         <v>7.3460884777581392E-2</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <f t="shared" si="12"/>
         <v>4086839150708.9219</v>
       </c>
@@ -4933,11 +4918,11 @@
       <c r="A84" s="1">
         <v>44105</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="9">
         <f t="shared" si="9"/>
         <v>8.2305584032677334E-2</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="10">
         <f t="shared" si="12"/>
         <v>4590034999471.3203</v>
       </c>
@@ -4978,11 +4963,11 @@
       <c r="A85" s="1">
         <v>44136</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="9">
         <f t="shared" si="9"/>
         <v>8.2421735045198549E-2</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <f t="shared" si="12"/>
         <v>4611869647634.2187</v>
       </c>
@@ -5023,11 +5008,11 @@
       <c r="A86" s="1">
         <v>44166</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="9">
         <f t="shared" si="9"/>
         <v>0.14721271531485253</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <f t="shared" si="12"/>
         <v>8282199354034.4609</v>
       </c>
@@ -5068,11 +5053,11 @@
       <c r="A87" s="1">
         <v>44197</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="9">
         <f t="shared" si="9"/>
         <v>6.2331817510241354E-2</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <f>E87</f>
         <v>3297723134317.5098</v>
       </c>
@@ -5113,11 +5098,11 @@
       <c r="A88" s="1">
         <v>44228</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="9">
         <f t="shared" si="9"/>
         <v>7.7621129437836597E-2</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <f>E88-E87</f>
         <v>4140954776377.6104</v>
       </c>
@@ -5158,11 +5143,11 @@
       <c r="A89" s="1">
         <v>44256</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="9">
         <f t="shared" si="9"/>
         <v>8.0485931921195991E-2</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <f t="shared" ref="C89:C98" si="13">E89-E88</f>
         <v>4341036228829.1807</v>
       </c>
@@ -5203,11 +5188,11 @@
       <c r="A90" s="1">
         <v>44287</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="9">
         <f t="shared" si="9"/>
         <v>9.9905982406166993E-2</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <f t="shared" si="13"/>
         <v>5436166487427.209</v>
       </c>
@@ -5248,11 +5233,11 @@
       <c r="A91" s="1">
         <v>44317</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="9">
         <f t="shared" si="9"/>
         <v>6.6417756540477726E-2</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <f t="shared" si="13"/>
         <v>3628872606629.2402</v>
       </c>
@@ -5293,11 +5278,11 @@
       <c r="A92" s="1">
         <v>44348</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="9">
         <f t="shared" si="9"/>
         <v>7.6848419347335412E-2</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <f t="shared" si="13"/>
         <v>4227682560314.1797</v>
       </c>
@@ -5338,11 +5323,11 @@
       <c r="A93" s="1">
         <v>44378</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="9">
         <f t="shared" si="9"/>
         <v>8.5000545071801908E-2</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <f t="shared" si="13"/>
         <v>4793005970491.918</v>
       </c>
@@ -5383,11 +5368,11 @@
       <c r="A94" s="1">
         <v>44409</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="9">
         <f t="shared" si="9"/>
         <v>9.1046742313048365E-2</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <f t="shared" si="13"/>
         <v>5208111752847.6133</v>
       </c>
@@ -5428,11 +5413,11 @@
       <c r="A95" s="1">
         <v>44440</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="9">
         <f t="shared" si="9"/>
         <v>7.5996192674584059E-2</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <f t="shared" si="13"/>
         <v>4358938399210.9219</v>
       </c>
@@ -5473,11 +5458,11 @@
       <c r="A96" s="1">
         <v>44470</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="9">
         <f t="shared" si="9"/>
         <v>7.9068355380497252E-2</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <f t="shared" si="13"/>
         <v>4679822055855.9375</v>
       </c>
@@ -5518,11 +5503,11 @@
       <c r="A97" s="1">
         <v>44501</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="9">
         <f t="shared" si="9"/>
         <v>7.5846644170129748E-2</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <f t="shared" si="13"/>
         <v>4511271951273.2422</v>
       </c>
@@ -5563,11 +5548,11 @@
       <c r="A98" s="1">
         <v>44531</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="9">
         <f t="shared" si="9"/>
         <v>0.16269016325653413</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="10">
         <f t="shared" si="13"/>
         <v>9846771534780.3047</v>
       </c>
@@ -5608,11 +5593,11 @@
       <c r="A99" s="1">
         <v>44562</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="9">
         <f t="shared" si="9"/>
         <v>6.0123570694655307E-2</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <f>E99</f>
         <v>3523455180606.4897</v>
       </c>
@@ -5653,11 +5638,11 @@
       <c r="A100" s="1">
         <v>44593</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="9">
         <f t="shared" si="9"/>
         <v>7.5394250119116824E-2</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <f>E100-E99</f>
         <v>4452750104386.6816</v>
       </c>
@@ -5698,11 +5683,11 @@
       <c r="A101" s="1">
         <v>44621</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="9">
         <f t="shared" si="9"/>
         <v>9.2485378902964863E-2</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <f t="shared" ref="C101:C110" si="14">E101-E100</f>
         <v>5518738163254.5381</v>
       </c>
@@ -5743,11 +5728,11 @@
       <c r="A102" s="1">
         <v>44652</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="9">
         <f t="shared" si="9"/>
         <v>0.10414610231399568</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="10">
         <f t="shared" si="14"/>
         <v>6324208708959.9316</v>
       </c>
@@ -5788,11 +5773,11 @@
       <c r="A103" s="1">
         <v>44682</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="9">
         <f t="shared" si="9"/>
         <v>6.7917959755581125E-2</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <f t="shared" si="14"/>
         <v>4195630663426.0937</v>
       </c>
@@ -5833,11 +5818,11 @@
       <c r="A104" s="1">
         <v>44713</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="9">
         <f t="shared" si="9"/>
         <v>8.3404962587005332E-2</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="10">
         <f t="shared" si="14"/>
         <v>5222654723900.5547</v>
       </c>
@@ -5878,11 +5863,11 @@
       <c r="A105" s="1">
         <v>44743</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="9">
         <f t="shared" si="9"/>
         <v>8.9021270708338429E-2</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <f t="shared" si="14"/>
         <v>5729350096342.8594</v>
       </c>
@@ -5923,11 +5908,11 @@
       <c r="A106" s="1">
         <v>44774</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="9">
         <f t="shared" si="9"/>
         <v>7.6450296248725721E-2</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="10">
         <f t="shared" si="14"/>
         <v>4948904344701.6406</v>
       </c>
@@ -5968,11 +5953,11 @@
       <c r="A107" s="1">
         <v>44805</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="9">
         <f t="shared" si="9"/>
         <v>7.9563414773373073E-2</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <f t="shared" si="14"/>
         <v>5202193825299.3984</v>
       </c>
@@ -6013,11 +5998,11 @@
       <c r="A108" s="1">
         <v>44835</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="9">
         <f t="shared" si="9"/>
         <v>8.1156040454319123E-2</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <f t="shared" si="14"/>
         <v>5360779485816.7266</v>
       </c>
@@ -6058,11 +6043,11 @@
       <c r="A109" s="1">
         <v>44866</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="9">
         <f t="shared" si="9"/>
         <v>8.1688612139321298E-2</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <f t="shared" si="14"/>
         <v>5493286704251.6328</v>
       </c>
@@ -6103,11 +6088,11 @@
       <c r="A110" s="1">
         <v>44896</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="9">
         <f t="shared" si="9"/>
         <v>0.17871302227252514</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <f t="shared" si="14"/>
         <v>12817191271773.68</v>
       </c>
@@ -6148,11 +6133,11 @@
       <c r="A111" s="1">
         <v>44927</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="9">
         <f t="shared" si="9"/>
         <v>6.8768126300349341E-2</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <f>E111</f>
         <v>4776386403213.9805</v>
       </c>
@@ -6193,11 +6178,11 @@
       <c r="A112" s="1">
         <v>44958</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="9">
         <f t="shared" si="9"/>
         <v>7.9988471740537012E-2</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <f>E112-E111</f>
         <v>5605645289228.1895</v>
       </c>
@@ -6238,11 +6223,11 @@
       <c r="A113" s="1">
         <v>44986</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="9">
         <f t="shared" si="9"/>
         <v>7.9187830976930634E-2</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <f t="shared" ref="C113:C122" si="15">E113-E112</f>
         <v>5640122879585.0996</v>
       </c>
@@ -6283,11 +6268,11 @@
       <c r="A114" s="1">
         <v>45017</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="9">
         <f t="shared" si="9"/>
         <v>9.0072732359786467E-2</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="10">
         <f t="shared" si="15"/>
         <v>6395557052167.1523</v>
       </c>
@@ -6328,11 +6313,11 @@
       <c r="A115" s="1">
         <v>45047</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="9">
         <f t="shared" si="9"/>
         <v>7.4961740919082934E-2</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <f t="shared" si="15"/>
         <v>5343103127186.75</v>
       </c>
@@ -6373,11 +6358,11 @@
       <c r="A116" s="1">
         <v>45078</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="9">
         <f t="shared" si="9"/>
         <v>7.7816272055573399E-2</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="10">
         <f t="shared" si="15"/>
         <v>5617660784688.5508</v>
       </c>
@@ -6418,11 +6403,11 @@
       <c r="A117" s="1">
         <v>45108</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="9">
         <f t="shared" si="9"/>
         <v>7.7440059529534269E-2</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <f t="shared" si="15"/>
         <v>5569461322961.3711</v>
       </c>
@@ -6463,11 +6448,11 @@
       <c r="A118" s="1">
         <v>45139</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="9">
         <f t="shared" si="9"/>
         <v>7.3087256638571546E-2</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <f t="shared" si="15"/>
         <v>5279660535853.5625</v>
       </c>
@@ -6508,11 +6493,11 @@
       <c r="A119" s="1">
         <v>45170</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="9">
         <f t="shared" si="9"/>
         <v>7.8871897036683944E-2</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <f t="shared" si="15"/>
         <v>5773400934504.0547</v>
       </c>
@@ -6553,11 +6538,11 @@
       <c r="A120" s="1">
         <v>45200</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="9">
         <f t="shared" si="9"/>
         <v>8.0512246781033414E-2</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="10">
         <f t="shared" si="15"/>
         <v>6036909236772.1641</v>
       </c>
@@ -6598,11 +6583,11 @@
       <c r="A121" s="1">
         <v>45231</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="9">
         <f t="shared" si="9"/>
         <v>8.0334431218297059E-2</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <f t="shared" si="15"/>
         <v>6061138384257.5078</v>
       </c>
@@ -6643,11 +6628,11 @@
       <c r="A122" s="1">
         <v>45261</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="9">
         <f t="shared" si="9"/>
         <v>0.16607281065064169</v>
       </c>
-      <c r="C122" s="11">
+      <c r="C122" s="10">
         <f t="shared" si="15"/>
         <v>12808942845341.945</v>
       </c>
@@ -6688,11 +6673,11 @@
       <c r="A123" s="1">
         <v>45292</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="9">
         <f t="shared" si="9"/>
         <v>5.7342660144534346E-2</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <f>E123</f>
         <v>4763002960354.9902</v>
       </c>
@@ -6733,11 +6718,11 @@
       <c r="A124" s="1">
         <v>45323</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="9">
         <f t="shared" si="9"/>
         <v>8.5343777233465201E-2</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="10">
         <f>E124-E123</f>
         <v>7131204877431.3398</v>
       </c>
@@ -6778,11 +6763,11 @@
       <c r="A125" s="1">
         <v>45352</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="9">
         <f t="shared" si="9"/>
         <v>7.7041151409159611E-2</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <f t="shared" ref="C125:C134" si="16">E125-E124</f>
         <v>6530391315946.4824</v>
       </c>
@@ -6823,11 +6808,11 @@
       <c r="A126" s="1">
         <v>45383</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="9">
         <f t="shared" si="9"/>
         <v>9.0037308329422555E-2</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="10">
         <f t="shared" si="16"/>
         <v>7618391204335.5</v>
       </c>
@@ -6868,11 +6853,11 @@
       <c r="A127" s="1">
         <v>45413</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="9">
         <f t="shared" si="9"/>
         <v>7.052280380686006E-2</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <f t="shared" si="16"/>
         <v>5982910402741.7852</v>
       </c>
@@ -6913,11 +6898,11 @@
       <c r="A128" s="1">
         <v>45444</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="9">
         <f t="shared" si="9"/>
         <v>7.6879180006008116E-2</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="10">
         <f t="shared" si="16"/>
         <v>6587577765411.668</v>
       </c>
@@ -6958,11 +6943,11 @@
       <c r="A129" s="1">
         <v>45474</v>
       </c>
-      <c r="B129" s="10">
+      <c r="B129" s="9">
         <f t="shared" si="9"/>
         <v>7.8311112476526196E-2</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <f t="shared" si="16"/>
         <v>6740454778281.3828</v>
       </c>
@@ -7003,11 +6988,11 @@
       <c r="A130" s="1">
         <v>45505</v>
       </c>
-      <c r="B130" s="10">
+      <c r="B130" s="9">
         <f t="shared" si="9"/>
         <v>6.8358568251853047E-2</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="10">
         <f t="shared" si="16"/>
         <v>5907520133150.1016</v>
       </c>
@@ -7048,11 +7033,11 @@
       <c r="A131" s="1">
         <v>45536</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="9">
         <f t="shared" si="9"/>
         <v>7.7979962782986953E-2</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <f t="shared" si="16"/>
         <v>6806354936893.25</v>
       </c>
@@ -7093,20 +7078,20 @@
       <c r="A132" s="1">
         <v>45566</v>
       </c>
-      <c r="B132" s="10">
-        <f t="shared" ref="B132:B144" si="17">C132/D132</f>
+      <c r="B132" s="9">
+        <f t="shared" ref="B132:B147" si="17">C132/D132</f>
         <v>8.9177031109468854E-2</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="10">
         <f t="shared" si="16"/>
         <v>7793806716341.5469</v>
       </c>
       <c r="D132" s="6">
-        <f t="shared" ref="D132:D146" si="18">SUM(F132,H132,J132,L132)</f>
+        <f t="shared" ref="D132:D147" si="18">SUM(F132,H132,J132,L132)</f>
         <v>87397019382427.016</v>
       </c>
       <c r="E132" s="6">
-        <f t="shared" ref="E132:E146" si="19">SUM(G132,I132,K132,M132)</f>
+        <f t="shared" ref="E132:E147" si="19">SUM(G132,I132,K132,M132)</f>
         <v>65861615090888.047</v>
       </c>
       <c r="F132" s="8">
@@ -7138,11 +7123,11 @@
       <c r="A133" s="1">
         <v>45597</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="9">
         <f t="shared" si="17"/>
         <v>8.0270874053172209E-2</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <f t="shared" si="16"/>
         <v>7157362797465.7812</v>
       </c>
@@ -7183,11 +7168,11 @@
       <c r="A134" s="1">
         <v>45627</v>
       </c>
-      <c r="B134" s="10">
+      <c r="B134" s="9">
         <f t="shared" si="17"/>
         <v>0.17193466532131893</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="10">
         <f t="shared" si="16"/>
         <v>15699648573874.562</v>
       </c>
@@ -7228,11 +7213,11 @@
       <c r="A135" s="1">
         <v>45658</v>
       </c>
-      <c r="B135" s="10">
+      <c r="B135" s="9">
         <f t="shared" si="17"/>
         <v>7.2243802225561718E-2</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <f>E135</f>
         <v>6750296454493.1904</v>
       </c>
@@ -7273,11 +7258,11 @@
       <c r="A136" s="1">
         <v>45689</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="9">
         <f t="shared" si="17"/>
         <v>8.1476338520044017E-2</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="10">
         <f>E136-E135</f>
         <v>7656135268630.4893</v>
       </c>
@@ -7318,12 +7303,12 @@
       <c r="A137" s="1">
         <v>45717</v>
       </c>
-      <c r="B137" s="10">
+      <c r="B137" s="9">
         <f t="shared" si="17"/>
         <v>7.8387946737700595E-2</v>
       </c>
-      <c r="C137" s="11">
-        <f t="shared" ref="C137:C146" si="20">E137-E136</f>
+      <c r="C137" s="10">
+        <f t="shared" ref="C137:C140" si="20">E137-E136</f>
         <v>7404644029646.6328</v>
       </c>
       <c r="D137" s="6">
@@ -7363,11 +7348,11 @@
       <c r="A138" s="1">
         <v>45748</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="9">
         <f t="shared" si="17"/>
         <v>9.7584054469967499E-2</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="10">
         <f t="shared" si="20"/>
         <v>9252143507484.7266</v>
       </c>
@@ -7408,11 +7393,11 @@
       <c r="A139" s="1">
         <v>45778</v>
       </c>
-      <c r="B139" s="10">
+      <c r="B139" s="9">
         <f t="shared" si="17"/>
         <v>6.6134434420464197E-2</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <f t="shared" si="20"/>
         <v>6290966379447.2344</v>
       </c>
@@ -7453,11 +7438,11 @@
       <c r="A140" s="1">
         <v>45809</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="9">
         <f t="shared" si="17"/>
         <v>7.8868374513177547E-2</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="10">
         <f t="shared" si="20"/>
         <v>7590433156532.9922</v>
       </c>
@@ -7498,12 +7483,12 @@
       <c r="A141" s="1">
         <v>45839</v>
       </c>
-      <c r="B141" s="10">
+      <c r="B141" s="9">
         <f t="shared" si="17"/>
         <v>8.8768035089126451E-2</v>
       </c>
-      <c r="C141" s="11">
-        <f t="shared" si="20"/>
+      <c r="C141" s="10">
+        <f>E141-E140</f>
         <v>8591455653164.0391</v>
       </c>
       <c r="D141" s="6">
@@ -7539,89 +7524,133 @@
         <v>2134527188248.5</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="1">
         <v>45870</v>
       </c>
-      <c r="B142" s="9"/>
-      <c r="C142" s="6"/>
+      <c r="B142" s="9">
+        <f t="shared" si="17"/>
+        <v>6.9833064832853925E-2</v>
+      </c>
+      <c r="C142" s="10">
+        <f t="shared" ref="C142:C145" si="21">E142-E141</f>
+        <v>6773804683013.2656</v>
+      </c>
       <c r="D142" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>96999962685676.594</v>
       </c>
       <c r="E142" s="6">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="8"/>
-      <c r="J142" s="8"/>
-      <c r="K142" s="8"/>
-      <c r="L142" s="8"/>
-      <c r="M142" s="8"/>
-    </row>
-    <row r="143" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>60309879132412.57</v>
+      </c>
+      <c r="F142" s="8">
+        <v>42962447026900</v>
+      </c>
+      <c r="G142" s="8">
+        <v>27659818607722.102</v>
+      </c>
+      <c r="H142" s="8">
+        <v>21625163465500</v>
+      </c>
+      <c r="I142" s="8">
+        <v>13916087391561.9</v>
+      </c>
+      <c r="J142" s="8">
+        <v>28391560384540</v>
+      </c>
+      <c r="K142" s="8">
+        <v>16282754303103.4</v>
+      </c>
+      <c r="L142" s="8">
+        <v>4020791808736.6001</v>
+      </c>
+      <c r="M142" s="8">
+        <v>2451218830025.1699</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="1">
         <v>45901</v>
       </c>
-      <c r="B143" s="9"/>
-      <c r="C143" s="6"/>
+      <c r="B143" s="9">
+        <f t="shared" si="17"/>
+        <v>7.151867080301548E-2</v>
+      </c>
+      <c r="C143" s="10">
+        <f t="shared" si="21"/>
+        <v>6952846279569.5469</v>
+      </c>
       <c r="D143" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>97217218965378.062</v>
       </c>
       <c r="E143" s="6">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="8"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="8"/>
-      <c r="L143" s="8"/>
-      <c r="M143" s="8"/>
-    </row>
-    <row r="144" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>67262725411982.117</v>
+      </c>
+      <c r="F143" s="8">
+        <v>42964555538800</v>
+      </c>
+      <c r="G143" s="8">
+        <v>30424132062211.398</v>
+      </c>
+      <c r="H143" s="8">
+        <v>21633870122700</v>
+      </c>
+      <c r="I143" s="8">
+        <v>15713189049438.5</v>
+      </c>
+      <c r="J143" s="8">
+        <v>28596846565342.102</v>
+      </c>
+      <c r="K143" s="8">
+        <v>18362516457723.102</v>
+      </c>
+      <c r="L143" s="8">
+        <v>4021946738535.9702</v>
+      </c>
+      <c r="M143" s="8">
+        <v>2762887842609.1201</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="1">
         <v>45931</v>
       </c>
       <c r="B144" s="9">
         <f t="shared" si="17"/>
-        <v>6.5655362542398663E-2</v>
-      </c>
-      <c r="C144" s="6">
-        <f t="shared" si="20"/>
-        <v>3087623548900.0498</v>
+        <v>8.2159133948359817E-2</v>
+      </c>
+      <c r="C144" s="10">
+        <f t="shared" si="21"/>
+        <v>8028840159940.0234</v>
       </c>
       <c r="D144" s="6">
         <f t="shared" si="18"/>
-        <v>47027743497816.141</v>
+        <v>97723037891154.734</v>
       </c>
       <c r="E144" s="6">
         <f t="shared" si="19"/>
-        <v>3087623548900.0498</v>
+        <v>75291565571922.141</v>
       </c>
       <c r="F144" s="8">
         <v>42992507529400</v>
       </c>
-      <c r="G144" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H144" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I144" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J144" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K144" s="8" t="s">
-        <v>12</v>
+      <c r="G144" s="8">
+        <v>33881799545304.102</v>
+      </c>
+      <c r="H144" s="8">
+        <v>21859811479300</v>
+      </c>
+      <c r="I144" s="8">
+        <v>17586741067765.5</v>
+      </c>
+      <c r="J144" s="8">
+        <v>28835482914038.602</v>
+      </c>
+      <c r="K144" s="8">
+        <v>20735401409952.5</v>
       </c>
       <c r="L144" s="8">
         <v>4035235968416.1401</v>
@@ -7630,37 +7659,139 @@
         <v>3087623548900.0498</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="1">
         <v>45962</v>
       </c>
-      <c r="B145" s="9"/>
-      <c r="C145" s="6"/>
+      <c r="B145" s="9">
+        <f t="shared" si="17"/>
+        <v>7.6115829444051361E-2</v>
+      </c>
+      <c r="C145" s="10">
+        <f t="shared" si="21"/>
+        <v>7450931413834.2969</v>
+      </c>
       <c r="D145" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>97889380806275.969</v>
       </c>
       <c r="E145" s="6">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>82742496985756.437</v>
+      </c>
+      <c r="F145" s="8">
+        <v>43007834175100</v>
+      </c>
+      <c r="G145" s="8">
+        <v>36955764061612.703</v>
+      </c>
+      <c r="H145" s="8">
+        <v>21921179778400</v>
+      </c>
+      <c r="I145" s="8">
+        <v>19349249659060.398</v>
+      </c>
+      <c r="J145" s="8">
+        <v>28918354751429.199</v>
+      </c>
+      <c r="K145" s="8">
+        <v>22998279367361</v>
+      </c>
+      <c r="L145" s="8">
+        <v>4042012101346.7598</v>
+      </c>
+      <c r="M145" s="8">
+        <v>3439203897722.3398</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="1">
         <v>45992</v>
       </c>
-      <c r="B146" s="9"/>
-      <c r="C146" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
+      <c r="B146" s="9">
+        <f t="shared" si="17"/>
+        <v>0.13645132238333721</v>
+      </c>
+      <c r="C146" s="10">
+        <f>E146-E145</f>
+        <v>13442409002708.203</v>
       </c>
       <c r="D146" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>98514318277869.078</v>
       </c>
       <c r="E146" s="6">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>96184905988464.641</v>
+      </c>
+      <c r="F146" s="8">
+        <v>43367142783700</v>
+      </c>
+      <c r="G146" s="8">
+        <v>42909204451656</v>
+      </c>
+      <c r="H146" s="8">
+        <v>22171600910100</v>
+      </c>
+      <c r="I146" s="8">
+        <v>21963437768993.699</v>
+      </c>
+      <c r="J146" s="8">
+        <v>28923970445017.102</v>
+      </c>
+      <c r="K146" s="8">
+        <v>27397248058089</v>
+      </c>
+      <c r="L146" s="8">
+        <v>4051604139051.98</v>
+      </c>
+      <c r="M146" s="8">
+        <v>3915015709725.9302</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A147" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B147" s="9">
+        <f t="shared" si="17"/>
+        <v>6.5899804802802053E-2</v>
+      </c>
+      <c r="C147" s="6">
+        <f>E147</f>
+        <v>6654820783412.5898</v>
+      </c>
+      <c r="D147" s="6">
+        <f t="shared" si="18"/>
+        <v>100983922537045.62</v>
+      </c>
+      <c r="E147" s="6">
+        <f t="shared" si="19"/>
+        <v>6654820783412.5898</v>
+      </c>
+      <c r="F147" s="8">
+        <v>44441279186100</v>
+      </c>
+      <c r="G147" s="8">
+        <v>3993270936622.8398</v>
+      </c>
+      <c r="H147" s="8">
+        <v>23596904071500</v>
+      </c>
+      <c r="I147" s="8">
+        <v>1154446765196.6101</v>
+      </c>
+      <c r="J147" s="8">
+        <v>28679324784314.801</v>
+      </c>
+      <c r="K147" s="8">
+        <v>1291567596698.8301</v>
+      </c>
+      <c r="L147" s="8">
+        <v>4266414495130.8301</v>
+      </c>
+      <c r="M147" s="8">
+        <v>215535484894.31</v>
       </c>
     </row>
   </sheetData>
@@ -7678,7 +7809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -7690,13 +7821,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
@@ -7709,10 +7840,10 @@
       <c r="A2" s="1">
         <v>41640</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>4.455966420199349E-2</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1452808895239.28</v>
       </c>
       <c r="D2" s="6">
@@ -7726,10 +7857,10 @@
       <c r="A3" s="1">
         <v>41671</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>8.7318170049497726E-2</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>2855916288926.6201</v>
       </c>
       <c r="D3" s="6">
@@ -7743,10 +7874,10 @@
       <c r="A4" s="1">
         <v>41699</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>7.5680716935203618E-2</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>2493370755431.5903</v>
       </c>
       <c r="D4" s="6">
@@ -7760,10 +7891,10 @@
       <c r="A5" s="1">
         <v>41730</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>8.7840193045120599E-2</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>2924844680409.8613</v>
       </c>
       <c r="D5" s="6">
@@ -7777,10 +7908,10 @@
       <c r="A6" s="1">
         <v>41760</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>6.4943332025611464E-2</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>2174666553888.6797</v>
       </c>
       <c r="D6" s="6">
@@ -7794,10 +7925,10 @@
       <c r="A7" s="1">
         <v>41791</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>7.486436229124413E-2</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>2516168151501.3691</v>
       </c>
       <c r="D7" s="6">
@@ -7811,10 +7942,10 @@
       <c r="A8" s="1">
         <v>41821</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>7.9109253097964835E-2</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>2667163008233.5605</v>
       </c>
       <c r="D8" s="6">
@@ -7828,10 +7959,10 @@
       <c r="A9" s="1">
         <v>41852</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>7.0990945372778919E-2</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>2398723873756.4297</v>
       </c>
       <c r="D9" s="6">
@@ -7845,10 +7976,10 @@
       <c r="A10" s="1">
         <v>41883</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>7.5191642969707859E-2</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>2547722724138.7734</v>
       </c>
       <c r="D10" s="6">
@@ -7862,10 +7993,10 @@
       <c r="A11" s="1">
         <v>41913</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>8.5505353459643052E-2</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>2901961405430.7656</v>
       </c>
       <c r="D11" s="6">
@@ -7879,10 +8010,10 @@
       <c r="A12" s="1">
         <v>41944</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>7.015055606896374E-2</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>2383569938670.1484</v>
       </c>
       <c r="D12" s="6">
@@ -7896,10 +8027,10 @@
       <c r="A13" s="1">
         <v>41974</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>0.16937139917747276</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>5932401498120.543</v>
       </c>
       <c r="D13" s="6">
@@ -7913,10 +8044,10 @@
       <c r="A14" s="1">
         <v>42005</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>6.7308481627115085E-2</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>2447081435343.3701</v>
       </c>
       <c r="D14" s="6">
@@ -7930,10 +8061,10 @@
       <c r="A15" s="1">
         <v>42036</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>7.9218046152364899E-2</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>2885909717401.5098</v>
       </c>
       <c r="D15" s="6">
@@ -7947,10 +8078,10 @@
       <c r="A16" s="1">
         <v>42064</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>7.569905212068502E-2</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>2779488709348.9297</v>
       </c>
       <c r="D16" s="6">
@@ -7964,10 +8095,10 @@
       <c r="A17" s="1">
         <v>42095</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>9.9435929331961576E-2</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>3633684010619.7197</v>
       </c>
       <c r="D17" s="6">
@@ -7981,10 +8112,10 @@
       <c r="A18" s="1">
         <v>42125</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>6.3413259412510664E-2</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>2334857093067.6309</v>
       </c>
       <c r="D18" s="6">
@@ -7998,10 +8129,10 @@
       <c r="A19" s="1">
         <v>42156</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>7.6707905535151888E-2</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>2834589813444.4609</v>
       </c>
       <c r="D19" s="6">
@@ -8015,10 +8146,10 @@
       <c r="A20" s="1">
         <v>42186</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>8.4243417369598644E-2</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>3120073809589.5781</v>
       </c>
       <c r="D20" s="6">
@@ -8032,10 +8163,10 @@
       <c r="A21" s="1">
         <v>42217</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>7.0458064891046238E-2</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>2613769491650.875</v>
       </c>
       <c r="D21" s="6">
@@ -8049,10 +8180,10 @@
       <c r="A22" s="1">
         <v>42248</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>6.87075732368677E-2</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>2553986032160.3164</v>
       </c>
       <c r="D22" s="6">
@@ -8066,10 +8197,10 @@
       <c r="A23" s="1">
         <v>42278</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>7.5784362901564956E-2</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>2824039575607.293</v>
       </c>
       <c r="D23" s="6">
@@ -8083,10 +8214,10 @@
       <c r="A24" s="1">
         <v>42309</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>7.0834342921987994E-2</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>2661255834701.2148</v>
       </c>
       <c r="D24" s="6">
@@ -8100,10 +8231,10 @@
       <c r="A25" s="1">
         <v>42339</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>0.14542702922387979</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>5494857451528.3437</v>
       </c>
       <c r="D25" s="6">
@@ -8117,10 +8248,10 @@
       <c r="A26" s="1">
         <v>42370</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>4.5102894272130517E-2</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>1674872672706.8899</v>
       </c>
       <c r="D26" s="6">
@@ -8134,10 +8265,10 @@
       <c r="A27" s="1">
         <v>42401</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>7.5476699104046918E-2</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>2810642618042.7402</v>
       </c>
       <c r="D27" s="6">
@@ -8151,10 +8282,10 @@
       <c r="A28" s="1">
         <v>42430</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>9.4514353441502205E-2</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>3541161805021.5889</v>
       </c>
       <c r="D28" s="6">
@@ -8168,10 +8299,10 @@
       <c r="A29" s="1">
         <v>42461</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>8.9249124192946755E-2</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>3363111052687.5605</v>
       </c>
       <c r="D29" s="6">
@@ -8185,10 +8316,10 @@
       <c r="A30" s="1">
         <v>42491</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>6.8815823620138078E-2</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <v>2608444530970.3008</v>
       </c>
       <c r="D30" s="6">
@@ -8202,10 +8333,10 @@
       <c r="A31" s="1">
         <v>42522</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>7.9644534649893281E-2</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>3034426495565.5078</v>
       </c>
       <c r="D31" s="6">
@@ -8219,10 +8350,10 @@
       <c r="A32" s="1">
         <v>42552</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>7.2922086652311521E-2</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="10">
         <v>2786218866898.502</v>
       </c>
       <c r="D32" s="6">
@@ -8236,10 +8367,10 @@
       <c r="A33" s="1">
         <v>42583</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>7.5233423631754406E-2</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>2887938189341.082</v>
       </c>
       <c r="D33" s="6">
@@ -8253,10 +8384,10 @@
       <c r="A34" s="1">
         <v>42614</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>7.6221359983037792E-2</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>2932328694406.2461</v>
       </c>
       <c r="D34" s="6">
@@ -8270,10 +8401,10 @@
       <c r="A35" s="1">
         <v>42644</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>7.4471984938858871E-2</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>2870491510236.1328</v>
       </c>
       <c r="D35" s="6">
@@ -8287,10 +8418,10 @@
       <c r="A36" s="1">
         <v>42675</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>7.7474411879997124E-2</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>3020797872971.9687</v>
       </c>
       <c r="D36" s="6">
@@ -8304,10 +8435,10 @@
       <c r="A37" s="1">
         <v>42705</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>0.15641049509014004</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>6097625439857.3945</v>
       </c>
       <c r="D37" s="6">
@@ -8321,10 +8452,10 @@
       <c r="A38" s="1">
         <v>42736</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>6.5213786491388634E-2</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>2548036804399.2803</v>
       </c>
       <c r="D38" s="6">
@@ -8338,10 +8469,10 @@
       <c r="A39" s="1">
         <v>42767</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>7.0010286595203627E-2</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>2758284210988.2803</v>
       </c>
       <c r="D39" s="6">
@@ -8355,10 +8486,10 @@
       <c r="A40" s="1">
         <v>42795</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>8.7740425904915376E-2</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>3488515388403.8887</v>
       </c>
       <c r="D40" s="6">
@@ -8372,10 +8503,10 @@
       <c r="A41" s="1">
         <v>42826</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>8.0831877976049862E-2</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>3229251332713.5605</v>
       </c>
       <c r="D41" s="6">
@@ -8389,10 +8520,10 @@
       <c r="A42" s="1">
         <v>42856</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <v>7.140272906247902E-2</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>2862990975834.5</v>
       </c>
       <c r="D42" s="6">
@@ -8406,10 +8537,10 @@
       <c r="A43" s="1">
         <v>42887</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>7.7591925180026278E-2</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>3123182914928.0605</v>
       </c>
       <c r="D43" s="6">
@@ -8423,10 +8554,10 @@
       <c r="A44" s="1">
         <v>42917</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <v>7.319335854030623E-2</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>2981049809794.4102</v>
       </c>
       <c r="D44" s="6">
@@ -8440,10 +8571,10 @@
       <c r="A45" s="1">
         <v>42948</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>7.3283719354462915E-2</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>2986417566961.2695</v>
       </c>
       <c r="D45" s="6">
@@ -8457,10 +8588,10 @@
       <c r="A46" s="1">
         <v>42979</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>7.4234531073113827E-2</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>3028227531439.207</v>
       </c>
       <c r="D46" s="6">
@@ -8474,10 +8605,10 @@
       <c r="A47" s="1">
         <v>43009</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <v>7.7241316547473807E-2</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>3166479398422.168</v>
       </c>
       <c r="D47" s="6">
@@ -8491,10 +8622,10 @@
       <c r="A48" s="1">
         <v>43040</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <v>7.9594415245820963E-2</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <v>3276367817656.8203</v>
       </c>
       <c r="D48" s="6">
@@ -8508,10 +8639,10 @@
       <c r="A49" s="1">
         <v>43070</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <v>0.13978617922590339</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>5756568839572.25</v>
       </c>
       <c r="D49" s="6">
@@ -8525,10 +8656,10 @@
       <c r="A50" s="1">
         <v>43101</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <v>5.6407514622649244E-2</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>2330374601127.5801</v>
       </c>
       <c r="D50" s="6">
@@ -8542,10 +8673,10 @@
       <c r="A51" s="1">
         <v>43132</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <v>7.0195115779144182E-2</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>2926830443249.2598</v>
       </c>
       <c r="D51" s="6">
@@ -8559,10 +8690,10 @@
       <c r="A52" s="1">
         <v>43160</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <v>8.3449873953928236E-2</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>3499180452026.4609</v>
       </c>
       <c r="D52" s="6">
@@ -8576,10 +8707,10 @@
       <c r="A53" s="1">
         <v>43191</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <v>8.6163229955786333E-2</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>3628156461152.5996</v>
       </c>
       <c r="D53" s="6">
@@ -8593,10 +8724,10 @@
       <c r="A54" s="1">
         <v>43221</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <v>7.1745398493539239E-2</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>3035122679626.9883</v>
       </c>
       <c r="D54" s="6">
@@ -8610,10 +8741,10 @@
       <c r="A55" s="1">
         <v>43252</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <v>7.9304241856382088E-2</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>3364158715441.0957</v>
       </c>
       <c r="D55" s="6">
@@ -8627,10 +8758,10 @@
       <c r="A56" s="1">
         <v>43282</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <v>7.8605261869730797E-2</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>3353295043642.2031</v>
       </c>
       <c r="D56" s="6">
@@ -8644,10 +8775,10 @@
       <c r="A57" s="1">
         <v>43313</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <v>7.2354333512687094E-2</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>3088841839205.8711</v>
       </c>
       <c r="D57" s="6">
@@ -8661,10 +8792,10 @@
       <c r="A58" s="1">
         <v>43344</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <v>7.1394362151297311E-2</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>3053541107357.4531</v>
       </c>
       <c r="D58" s="6">
@@ -8678,10 +8809,10 @@
       <c r="A59" s="1">
         <v>43374</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <v>7.9153121714094568E-2</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>3396853509510.7773</v>
       </c>
       <c r="D59" s="6">
@@ -8695,10 +8826,10 @@
       <c r="A60" s="1">
         <v>43405</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <v>7.8046236354924359E-2</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="10">
         <v>3373280446982.9023</v>
       </c>
       <c r="D60" s="6">
@@ -8712,10 +8843,10 @@
       <c r="A61" s="1">
         <v>43435</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <v>0.14617618648683828</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>6325973719213.9492</v>
       </c>
       <c r="D61" s="6">
@@ -8729,10 +8860,10 @@
       <c r="A62" s="1">
         <v>43466</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="9">
         <v>5.3976626427885019E-2</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="10">
         <v>2424221190875.9199</v>
       </c>
       <c r="D62" s="6">
@@ -8746,10 +8877,10 @@
       <c r="A63" s="1">
         <v>43497</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <v>7.2400490429240169E-2</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>3289467666248.4199</v>
       </c>
       <c r="D63" s="6">
@@ -8763,10 +8894,10 @@
       <c r="A64" s="1">
         <v>43525</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="9">
         <v>7.6546318627117887E-2</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <v>3526864330788.8711</v>
       </c>
       <c r="D64" s="6">
@@ -8780,10 +8911,10 @@
       <c r="A65" s="1">
         <v>43556</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>8.767150958502469E-2</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>4056743029774.25</v>
       </c>
       <c r="D65" s="6">
@@ -8797,10 +8928,10 @@
       <c r="A66" s="1">
         <v>43586</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <v>6.2355825719220055E-2</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="10">
         <v>2894679737982.8887</v>
       </c>
       <c r="D66" s="6">
@@ -8814,10 +8945,10 @@
       <c r="A67" s="1">
         <v>43617</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>7.476900908643469E-2</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>3478627064916.5137</v>
       </c>
       <c r="D67" s="6">
@@ -8831,10 +8962,10 @@
       <c r="A68" s="1">
         <v>43647</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <v>7.9193454948139633E-2</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <v>3720981322215.5937</v>
       </c>
       <c r="D68" s="6">
@@ -8848,10 +8979,10 @@
       <c r="A69" s="1">
         <v>43678</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>7.1450607781841216E-2</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>3360651815314.5898</v>
       </c>
       <c r="D69" s="6">
@@ -8865,10 +8996,10 @@
       <c r="A70" s="1">
         <v>43709</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="9">
         <v>7.8265885346615646E-2</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="10">
         <v>3689489117938.4648</v>
       </c>
       <c r="D70" s="6">
@@ -8882,10 +9013,10 @@
       <c r="A71" s="1">
         <v>43739</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="9">
         <v>8.0963255749509924E-2</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>3828950163256.6016</v>
       </c>
       <c r="D71" s="6">
@@ -8899,10 +9030,10 @@
       <c r="A72" s="1">
         <v>43770</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="9">
         <v>7.8367729197036357E-2</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="10">
         <v>3712846679281.5195</v>
       </c>
       <c r="D72" s="6">
@@ -8916,10 +9047,10 @@
       <c r="A73" s="1">
         <v>43800</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="9">
         <v>0.15211768193004896</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>7244071323321.6172</v>
       </c>
       <c r="D73" s="6">
@@ -8933,10 +9064,10 @@
       <c r="A74" s="1">
         <v>43831</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="9">
         <v>6.226341166202172E-2</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <v>3081755006343.2695</v>
       </c>
       <c r="D74" s="6">
@@ -8950,10 +9081,10 @@
       <c r="A75" s="1">
         <v>43862</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <v>6.9662425802943961E-2</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>3481045383272.9199</v>
       </c>
       <c r="D75" s="6">
@@ -8967,10 +9098,10 @@
       <c r="A76" s="1">
         <v>43891</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>8.4101128889670224E-2</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <v>4284046296964.832</v>
       </c>
       <c r="D76" s="6">
@@ -8984,10 +9115,10 @@
       <c r="A77" s="1">
         <v>43922</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <v>9.1361743168674403E-2</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>4785979411202.0508</v>
       </c>
       <c r="D77" s="6">
@@ -9001,10 +9132,10 @@
       <c r="A78" s="1">
         <v>43952</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="9">
         <v>6.5239645228519369E-2</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="10">
         <v>3447076441944.166</v>
       </c>
       <c r="D78" s="6">
@@ -9018,10 +9149,10 @@
       <c r="A79" s="1">
         <v>43983</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="9">
         <v>8.9554766170601693E-2</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>4768676690284.7227</v>
       </c>
       <c r="D79" s="6">
@@ -9035,10 +9166,10 @@
       <c r="A80" s="1">
         <v>44013</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="9">
         <v>8.332830643090218E-2</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="10">
         <v>4451483705756.3086</v>
       </c>
       <c r="D80" s="6">
@@ -9052,10 +9183,10 @@
       <c r="A81" s="1">
         <v>44044</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="9">
         <v>6.8631240956743403E-2</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>3800678732572.0586</v>
       </c>
       <c r="D81" s="6">
@@ -9069,10 +9200,10 @@
       <c r="A82" s="1">
         <v>44075</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="9">
         <v>7.3460884777581392E-2</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="10">
         <v>4086839150708.9219</v>
       </c>
       <c r="D82" s="6">
@@ -9086,10 +9217,10 @@
       <c r="A83" s="1">
         <v>44105</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="9">
         <v>8.2305584032677334E-2</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>4590034999471.3203</v>
       </c>
       <c r="D83" s="6">
@@ -9103,10 +9234,10 @@
       <c r="A84" s="1">
         <v>44136</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="9">
         <v>8.2421735045198549E-2</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="10">
         <v>4611869647634.2187</v>
       </c>
       <c r="D84" s="6">
@@ -9120,10 +9251,10 @@
       <c r="A85" s="1">
         <v>44166</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="9">
         <v>0.14721271531485253</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>8282199354034.4609</v>
       </c>
       <c r="D85" s="6">
@@ -9137,10 +9268,10 @@
       <c r="A86" s="1">
         <v>44197</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="9">
         <v>6.2331817510241354E-2</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <v>3297723134317.5098</v>
       </c>
       <c r="D86" s="6">
@@ -9154,10 +9285,10 @@
       <c r="A87" s="1">
         <v>44228</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="9">
         <v>7.7621129437836597E-2</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>4140954776377.6104</v>
       </c>
       <c r="D87" s="6">
@@ -9171,10 +9302,10 @@
       <c r="A88" s="1">
         <v>44256</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="9">
         <v>8.0485931921195991E-2</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <v>4341036228829.1807</v>
       </c>
       <c r="D88" s="6">
@@ -9188,10 +9319,10 @@
       <c r="A89" s="1">
         <v>44287</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="9">
         <v>9.9905982406166993E-2</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>5436166487427.209</v>
       </c>
       <c r="D89" s="6">
@@ -9205,10 +9336,10 @@
       <c r="A90" s="1">
         <v>44317</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="9">
         <v>6.6417756540477726E-2</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <v>3628872606629.2402</v>
       </c>
       <c r="D90" s="6">
@@ -9222,10 +9353,10 @@
       <c r="A91" s="1">
         <v>44348</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="9">
         <v>7.6848419347335412E-2</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>4227682560314.1797</v>
       </c>
       <c r="D91" s="6">
@@ -9239,10 +9370,10 @@
       <c r="A92" s="1">
         <v>44378</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="9">
         <v>8.5000545071801908E-2</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>4793005970491.918</v>
       </c>
       <c r="D92" s="6">
@@ -9256,10 +9387,10 @@
       <c r="A93" s="1">
         <v>44409</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="9">
         <v>9.1046742313048365E-2</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>5208111752847.6133</v>
       </c>
       <c r="D93" s="6">
@@ -9273,10 +9404,10 @@
       <c r="A94" s="1">
         <v>44440</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="9">
         <v>7.5996192674584059E-2</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <v>4358938399210.9219</v>
       </c>
       <c r="D94" s="6">
@@ -9290,10 +9421,10 @@
       <c r="A95" s="1">
         <v>44470</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="9">
         <v>7.9068355380497252E-2</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>4679822055855.9375</v>
       </c>
       <c r="D95" s="6">
@@ -9307,10 +9438,10 @@
       <c r="A96" s="1">
         <v>44501</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="9">
         <v>7.5846644170129748E-2</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <v>4511271951273.2422</v>
       </c>
       <c r="D96" s="6">
@@ -9324,10 +9455,10 @@
       <c r="A97" s="1">
         <v>44531</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="9">
         <v>0.16269016325653413</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>9846771534780.3047</v>
       </c>
       <c r="D97" s="6">
@@ -9341,10 +9472,10 @@
       <c r="A98" s="1">
         <v>44562</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="9">
         <v>6.0123570694655307E-2</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="10">
         <v>3523455180606.4897</v>
       </c>
       <c r="D98" s="6">
@@ -9358,10 +9489,10 @@
       <c r="A99" s="1">
         <v>44593</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="9">
         <v>7.5394250119116824E-2</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>4452750104386.6816</v>
       </c>
       <c r="D99" s="6">
@@ -9375,10 +9506,10 @@
       <c r="A100" s="1">
         <v>44621</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="9">
         <v>9.2485378902964863E-2</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <v>5518738163254.5381</v>
       </c>
       <c r="D100" s="6">
@@ -9392,10 +9523,10 @@
       <c r="A101" s="1">
         <v>44652</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="9">
         <v>0.10414610231399568</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>6324208708959.9316</v>
       </c>
       <c r="D101" s="6">
@@ -9409,10 +9540,10 @@
       <c r="A102" s="1">
         <v>44682</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="9">
         <v>6.7917959755581125E-2</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="10">
         <v>4195630663426.0937</v>
       </c>
       <c r="D102" s="6">
@@ -9426,10 +9557,10 @@
       <c r="A103" s="1">
         <v>44713</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="9">
         <v>8.3404962587005332E-2</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>5222654723900.5547</v>
       </c>
       <c r="D103" s="6">
@@ -9443,10 +9574,10 @@
       <c r="A104" s="1">
         <v>44743</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="9">
         <v>8.9021270708338429E-2</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="10">
         <v>5729350096342.8594</v>
       </c>
       <c r="D104" s="6">
@@ -9460,10 +9591,10 @@
       <c r="A105" s="1">
         <v>44774</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="9">
         <v>7.6450296248725721E-2</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>4948904344701.6406</v>
       </c>
       <c r="D105" s="6">
@@ -9477,10 +9608,10 @@
       <c r="A106" s="1">
         <v>44805</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="9">
         <v>7.9563414773373073E-2</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="10">
         <v>5202193825299.3984</v>
       </c>
       <c r="D106" s="6">
@@ -9494,10 +9625,10 @@
       <c r="A107" s="1">
         <v>44835</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="9">
         <v>8.1156040454319123E-2</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>5360779485816.7266</v>
       </c>
       <c r="D107" s="6">
@@ -9511,10 +9642,10 @@
       <c r="A108" s="1">
         <v>44866</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="9">
         <v>8.1688612139321298E-2</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <v>5493286704251.6328</v>
       </c>
       <c r="D108" s="6">
@@ -9528,10 +9659,10 @@
       <c r="A109" s="1">
         <v>44896</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="9">
         <v>0.17871302227252514</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>12817191271773.68</v>
       </c>
       <c r="D109" s="6">
@@ -9545,10 +9676,10 @@
       <c r="A110" s="1">
         <v>44927</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="9">
         <v>6.8768126300349341E-2</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <v>4776386403213.9805</v>
       </c>
       <c r="D110" s="6">
@@ -9562,10 +9693,10 @@
       <c r="A111" s="1">
         <v>44958</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="9">
         <v>7.9988471740537012E-2</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>5605645289228.1895</v>
       </c>
       <c r="D111" s="6">
@@ -9579,10 +9710,10 @@
       <c r="A112" s="1">
         <v>44986</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="9">
         <v>7.9187830976930634E-2</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <v>5640122879585.0996</v>
       </c>
       <c r="D112" s="6">
@@ -9596,10 +9727,10 @@
       <c r="A113" s="1">
         <v>45017</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="9">
         <v>9.0072732359786467E-2</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>6395557052167.1523</v>
       </c>
       <c r="D113" s="6">
@@ -9613,10 +9744,10 @@
       <c r="A114" s="1">
         <v>45047</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="9">
         <v>7.4961740919082934E-2</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="10">
         <v>5343103127186.75</v>
       </c>
       <c r="D114" s="6">
@@ -9630,10 +9761,10 @@
       <c r="A115" s="1">
         <v>45078</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="9">
         <v>7.7816272055573399E-2</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>5617660784688.5508</v>
       </c>
       <c r="D115" s="6">
@@ -9647,10 +9778,10 @@
       <c r="A116" s="1">
         <v>45108</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="9">
         <v>7.7440059529534269E-2</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="10">
         <v>5569461322961.3711</v>
       </c>
       <c r="D116" s="6">
@@ -9664,10 +9795,10 @@
       <c r="A117" s="1">
         <v>45139</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="9">
         <v>7.3087256638571546E-2</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>5279660535853.5625</v>
       </c>
       <c r="D117" s="6">
@@ -9681,10 +9812,10 @@
       <c r="A118" s="1">
         <v>45170</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="9">
         <v>7.8871897036683944E-2</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <v>5773400934504.0547</v>
       </c>
       <c r="D118" s="6">
@@ -9698,10 +9829,10 @@
       <c r="A119" s="1">
         <v>45200</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="9">
         <v>8.0512246781033414E-2</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>6036909236772.1641</v>
       </c>
       <c r="D119" s="6">
@@ -9715,10 +9846,10 @@
       <c r="A120" s="1">
         <v>45231</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="9">
         <v>8.0334431218297059E-2</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="10">
         <v>6061138384257.5078</v>
       </c>
       <c r="D120" s="6">
@@ -9732,10 +9863,10 @@
       <c r="A121" s="1">
         <v>45261</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="9">
         <v>0.16607281065064169</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>12808942845341.945</v>
       </c>
       <c r="D121" s="6">
@@ -9749,10 +9880,10 @@
       <c r="A122" s="1">
         <v>45292</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="9">
         <v>5.7342660144534346E-2</v>
       </c>
-      <c r="C122" s="11">
+      <c r="C122" s="10">
         <v>4763002960354.9902</v>
       </c>
       <c r="D122" s="6">
@@ -9766,10 +9897,10 @@
       <c r="A123" s="1">
         <v>45323</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="9">
         <v>8.5343777233465201E-2</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <v>7131204877431.3398</v>
       </c>
       <c r="D123" s="6">
@@ -9783,10 +9914,10 @@
       <c r="A124" s="1">
         <v>45352</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="9">
         <v>7.7041151409159611E-2</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="10">
         <v>6530391315946.4824</v>
       </c>
       <c r="D124" s="6">
@@ -9800,10 +9931,10 @@
       <c r="A125" s="1">
         <v>45383</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="9">
         <v>9.0037308329422555E-2</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>7618391204335.5</v>
       </c>
       <c r="D125" s="6">
@@ -9817,10 +9948,10 @@
       <c r="A126" s="1">
         <v>45413</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="9">
         <v>7.052280380686006E-2</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="10">
         <v>5982910402741.7852</v>
       </c>
       <c r="D126" s="6">
@@ -9834,10 +9965,10 @@
       <c r="A127" s="1">
         <v>45444</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="9">
         <v>7.6879180006008116E-2</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>6587577765411.668</v>
       </c>
       <c r="D127" s="6">
@@ -9851,10 +9982,10 @@
       <c r="A128" s="1">
         <v>45474</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="9">
         <v>7.8311112476526196E-2</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="10">
         <v>6740454778281.3828</v>
       </c>
       <c r="D128" s="6">
@@ -9868,10 +9999,10 @@
       <c r="A129" s="1">
         <v>45505</v>
       </c>
-      <c r="B129" s="10">
+      <c r="B129" s="9">
         <v>6.8358568251853047E-2</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>5907520133150.1016</v>
       </c>
       <c r="D129" s="6">
@@ -9885,10 +10016,10 @@
       <c r="A130" s="1">
         <v>45536</v>
       </c>
-      <c r="B130" s="10">
+      <c r="B130" s="9">
         <v>7.7979962782986953E-2</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="10">
         <v>6806354936893.25</v>
       </c>
       <c r="D130" s="6">
@@ -9902,10 +10033,10 @@
       <c r="A131" s="1">
         <v>45566</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="9">
         <v>8.9177031109468854E-2</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>7793806716341.5469</v>
       </c>
       <c r="D131" s="6">
@@ -9919,10 +10050,10 @@
       <c r="A132" s="1">
         <v>45597</v>
       </c>
-      <c r="B132" s="10">
+      <c r="B132" s="9">
         <v>8.0270874053172209E-2</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="10">
         <v>7157362797465.7812</v>
       </c>
       <c r="D132" s="6">
@@ -9936,10 +10067,10 @@
       <c r="A133" s="1">
         <v>45627</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="9">
         <v>0.17193466532131893</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>15699648573874.562</v>
       </c>
       <c r="D133" s="6">
@@ -9953,10 +10084,10 @@
       <c r="A134" s="1">
         <v>45658</v>
       </c>
-      <c r="B134" s="10">
+      <c r="B134" s="9">
         <v>7.2243802225561718E-2</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="10">
         <v>6750296454493.1904</v>
       </c>
       <c r="D134" s="6">
@@ -9970,10 +10101,10 @@
       <c r="A135" s="1">
         <v>45689</v>
       </c>
-      <c r="B135" s="10">
+      <c r="B135" s="9">
         <v>8.1476338520044017E-2</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>7656135268630.4893</v>
       </c>
       <c r="D135" s="6">
@@ -9987,10 +10118,10 @@
       <c r="A136" s="1">
         <v>45717</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="9">
         <v>7.8387946737700595E-2</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="10">
         <v>7404644029646.6328</v>
       </c>
       <c r="D136" s="6">
@@ -10004,10 +10135,10 @@
       <c r="A137" s="1">
         <v>45748</v>
       </c>
-      <c r="B137" s="10">
+      <c r="B137" s="9">
         <v>9.7584054469967499E-2</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>9252143507484.7266</v>
       </c>
       <c r="D137" s="6">
@@ -10021,10 +10152,10 @@
       <c r="A138" s="1">
         <v>45778</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="9">
         <v>6.6134434420464197E-2</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="10">
         <v>6290966379447.2344</v>
       </c>
       <c r="D138" s="6">
@@ -10038,10 +10169,10 @@
       <c r="A139" s="1">
         <v>45809</v>
       </c>
-      <c r="B139" s="10">
+      <c r="B139" s="9">
         <v>7.8868374513177547E-2</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>7590433156532.9922</v>
       </c>
       <c r="D139" s="6">
@@ -10055,10 +10186,10 @@
       <c r="A140" s="1">
         <v>45839</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="9">
         <v>8.8768035089126451E-2</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="10">
         <v>8591455653164.0391</v>
       </c>
       <c r="D140" s="6">
@@ -10069,39 +10200,106 @@
       </c>
     </row>
     <row r="141" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="1"/>
-      <c r="B141" s="10"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
+      <c r="A141" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B141" s="9">
+        <v>6.9833064832853925E-2</v>
+      </c>
+      <c r="C141" s="10">
+        <v>6773804683013.2656</v>
+      </c>
+      <c r="D141" s="6">
+        <v>96999962685676.594</v>
+      </c>
+      <c r="E141" s="6">
+        <v>60309879132412.57</v>
+      </c>
     </row>
     <row r="142" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="1"/>
-      <c r="B142" s="10"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
+      <c r="A142" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B142" s="9">
+        <v>7.151867080301548E-2</v>
+      </c>
+      <c r="C142" s="10">
+        <v>6952846279569.5469</v>
+      </c>
+      <c r="D142" s="6">
+        <v>97217218965378.062</v>
+      </c>
+      <c r="E142" s="6">
+        <v>67262725411982.117</v>
+      </c>
     </row>
     <row r="143" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="1"/>
-      <c r="B143" s="10"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
+      <c r="A143" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B143" s="9">
+        <v>8.2159133948359817E-2</v>
+      </c>
+      <c r="C143" s="10">
+        <v>8028840159940.0234</v>
+      </c>
+      <c r="D143" s="6">
+        <v>97723037891154.734</v>
+      </c>
+      <c r="E143" s="6">
+        <v>75291565571922.141</v>
+      </c>
     </row>
     <row r="144" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="1"/>
-      <c r="B144" s="10"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-    </row>
-    <row r="145" spans="1:5" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A145" s="1"/>
-      <c r="B145" s="10"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
+      <c r="A144" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B144" s="9">
+        <v>7.6115829444051361E-2</v>
+      </c>
+      <c r="C144" s="10">
+        <v>7450931413834.2969</v>
+      </c>
+      <c r="D144" s="6">
+        <v>97889380806275.969</v>
+      </c>
+      <c r="E144" s="6">
+        <v>82742496985756.437</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B145" s="9">
+        <v>0.13645132238333721</v>
+      </c>
+      <c r="C145" s="10">
+        <v>13442409002708.203</v>
+      </c>
+      <c r="D145" s="6">
+        <v>98514318277869.078</v>
+      </c>
+      <c r="E145" s="6">
+        <v>96184905988464.641</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A146" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B146" s="9">
+        <v>6.5899804802802053E-2</v>
+      </c>
+      <c r="C146" s="10">
+        <v>6654820783412.5898</v>
+      </c>
+      <c r="D146" s="6">
+        <v>100983922537045.62</v>
+      </c>
+      <c r="E146" s="6">
+        <v>6654820783412.5898</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10122,18 +10320,18 @@
   <sheetData>
     <row r="1" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10141,10 +10339,10 @@
       <c r="A2" s="1">
         <v>41640</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>5.8758236449179102E-2</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1905201575075.74</v>
       </c>
       <c r="D2" s="6">
@@ -10158,10 +10356,10 @@
       <c r="A3" s="1">
         <v>41671</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>9.5907187620220602E-2</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>3136193025712.6499</v>
       </c>
       <c r="D3" s="6">
@@ -10175,10 +10373,10 @@
       <c r="A4" s="1">
         <v>41699</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>7.9744870227154693E-2</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>2623142419577.8799</v>
       </c>
       <c r="D4" s="6">
@@ -10192,10 +10390,10 @@
       <c r="A5" s="1">
         <v>41730</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>7.8786244374462203E-2</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>2617133735574.5098</v>
       </c>
       <c r="D5" s="6">
@@ -10209,10 +10407,10 @@
       <c r="A6" s="1">
         <v>41760</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>8.0668734274846596E-2</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>2702795523495.7402</v>
       </c>
       <c r="D6" s="6">
@@ -10226,10 +10424,10 @@
       <c r="A7" s="1">
         <v>41791</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>8.0557813570538706E-2</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>2712441541267.8198</v>
       </c>
       <c r="D7" s="6">
@@ -10243,10 +10441,10 @@
       <c r="A8" s="1">
         <v>41821</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>8.0321140679237901E-2</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>2708241925036.25</v>
       </c>
       <c r="D8" s="6">
@@ -10260,10 +10458,10 @@
       <c r="A9" s="1">
         <v>41852</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>8.3407508576303302E-2</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>2826223481891.23</v>
       </c>
       <c r="D9" s="6">
@@ -10277,10 +10475,10 @@
       <c r="A10" s="1">
         <v>41883</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>8.2110296236853397E-2</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>2792190020929.23</v>
       </c>
       <c r="D10" s="6">
@@ -10294,10 +10492,10 @@
       <c r="A11" s="1">
         <v>41913</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>8.6682263064983903E-2</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>2950888772115.52</v>
       </c>
       <c r="D11" s="6">
@@ -10311,10 +10509,10 @@
       <c r="A12" s="1">
         <v>41944</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>7.8760788820947905E-2</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>2692438336639.75</v>
       </c>
       <c r="D12" s="6">
@@ -10328,10 +10526,10 @@
       <c r="A13" s="1">
         <v>41974</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>8.7779597325933198E-2</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>3059226975525.21</v>
       </c>
       <c r="D13" s="6">
@@ -10345,10 +10543,10 @@
       <c r="A14" s="1">
         <v>42005</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>9.1303110717160102E-2</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>3305396348205.8101</v>
       </c>
       <c r="D14" s="6">
@@ -10362,10 +10560,10 @@
       <c r="A15" s="1">
         <v>42036</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>8.7011486141969602E-2</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>3169170566162.3198</v>
       </c>
       <c r="D15" s="6">
@@ -10379,10 +10577,10 @@
       <c r="A16" s="1">
         <v>42064</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>7.7538505154948006E-2</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>2838940731985.6299</v>
       </c>
       <c r="D16" s="6">
@@ -10396,10 +10594,10 @@
       <c r="A17" s="1">
         <v>42095</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>8.9186394340091901E-2</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>3251384299727.1899</v>
       </c>
       <c r="D17" s="6">
@@ -10413,10 +10611,10 @@
       <c r="A18" s="1">
         <v>42125</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>8.10285491745808E-2</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>2988965777503.8999</v>
       </c>
       <c r="D18" s="6">
@@ -10430,10 +10628,10 @@
       <c r="A19" s="1">
         <v>42156</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>8.0238460976346501E-2</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>2966662357672.3101</v>
       </c>
       <c r="D19" s="6">
@@ -10447,10 +10645,10 @@
       <c r="A20" s="1">
         <v>42186</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>8.5533689613254998E-2</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>3168117304645.9502</v>
       </c>
       <c r="D20" s="6">
@@ -10464,10 +10662,10 @@
       <c r="A21" s="1">
         <v>42217</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>8.2781420232905203E-2</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>3079592764037.4902</v>
       </c>
       <c r="D21" s="6">
@@ -10481,10 +10679,10 @@
       <c r="A22" s="1">
         <v>42248</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>7.5029416018725398E-2</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>2799045162961.8599</v>
       </c>
       <c r="D22" s="6">
@@ -10498,10 +10696,10 @@
       <c r="A23" s="1">
         <v>42278</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>7.9032628187874404E-2</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>2957835940154.5098</v>
       </c>
       <c r="D23" s="6">
@@ -10515,10 +10713,10 @@
       <c r="A24" s="1">
         <v>42309</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>7.73092625463144E-2</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>2918500727803.4199</v>
       </c>
       <c r="D24" s="6">
@@ -10532,10 +10730,10 @@
       <c r="A25" s="1">
         <v>42339</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>7.5370299047343894E-2</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>2833602871918.52</v>
       </c>
       <c r="D25" s="6">
@@ -10549,10 +10747,10 @@
       <c r="A26" s="1">
         <v>42370</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>6.2937918773618401E-2</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>2330255616343.8701</v>
       </c>
       <c r="D26" s="6">
@@ -10566,10 +10764,10 @@
       <c r="A27" s="1">
         <v>42401</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>7.9400340439455E-2</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>2955069644193.02</v>
       </c>
       <c r="D27" s="6">
@@ -10583,10 +10781,10 @@
       <c r="A28" s="1">
         <v>42430</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>9.4109226058063197E-2</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>3511494809054.7998</v>
       </c>
       <c r="D28" s="6">
@@ -10600,10 +10798,10 @@
       <c r="A29" s="1">
         <v>42461</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>8.2347142514027805E-2</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>3099590845224.2798</v>
       </c>
       <c r="D29" s="6">
@@ -10617,10 +10815,10 @@
       <c r="A30" s="1">
         <v>42491</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>8.5478279033878696E-2</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <v>3241897718737.77</v>
       </c>
       <c r="D30" s="6">
@@ -10634,10 +10832,10 @@
       <c r="A31" s="1">
         <v>42522</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>8.3309792587317494E-2</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>3175794191279.9102</v>
       </c>
       <c r="D31" s="6">
@@ -10651,10 +10849,10 @@
       <c r="A32" s="1">
         <v>42552</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>7.8349714752193197E-2</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="10">
         <v>3001470983480.6802</v>
       </c>
       <c r="D32" s="6">
@@ -10668,10 +10866,10 @@
       <c r="A33" s="1">
         <v>42583</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>8.3528802670535404E-2</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>3207240195175.0498</v>
       </c>
       <c r="D33" s="6">
@@ -10685,10 +10883,10 @@
       <c r="A34" s="1">
         <v>42614</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>8.3233780495592005E-2</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>3213658417908.52</v>
       </c>
       <c r="D34" s="6">
@@ -10702,10 +10900,10 @@
       <c r="A35" s="1">
         <v>42644</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>7.9892992967887003E-2</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>3096711323116.9502</v>
       </c>
       <c r="D35" s="6">
@@ -10719,10 +10917,10 @@
       <c r="A36" s="1">
         <v>42675</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>8.2196383030206405E-2</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>3216239757563.96</v>
       </c>
       <c r="D36" s="6">
@@ -10736,10 +10934,10 @@
       <c r="A37" s="1">
         <v>42705</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>8.3389013341774995E-2</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>3238796862672.52</v>
       </c>
       <c r="D37" s="6">
@@ -10753,10 +10951,10 @@
       <c r="A38" s="1">
         <v>42736</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>8.8463330470499493E-2</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>3441850335050.6099</v>
       </c>
       <c r="D38" s="6">
@@ -10770,10 +10968,10 @@
       <c r="A39" s="1">
         <v>42767</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>7.6900523850729693E-2</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>3029122258197.9199</v>
       </c>
       <c r="D39" s="6">
@@ -10787,10 +10985,10 @@
       <c r="A40" s="1">
         <v>42795</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>8.7364552908012594E-2</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>3459296308054.2798</v>
       </c>
       <c r="D40" s="6">
@@ -10804,10 +11002,10 @@
       <c r="A41" s="1">
         <v>42826</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>7.67214350374886E-2</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>3065540333213.2598</v>
       </c>
       <c r="D41" s="6">
@@ -10821,10 +11019,10 @@
       <c r="A42" s="1">
         <v>42856</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <v>8.6217075452555497E-2</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>3454588359168.3198</v>
       </c>
       <c r="D42" s="6">
@@ -10838,10 +11036,10 @@
       <c r="A43" s="1">
         <v>42887</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>8.1162331435555901E-2</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>3268672033001.04</v>
       </c>
       <c r="D43" s="6">
@@ -10855,10 +11053,10 @@
       <c r="A44" s="1">
         <v>42917</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <v>7.8640822366348104E-2</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>3211339706127.1899</v>
       </c>
       <c r="D44" s="6">
@@ -10872,10 +11070,10 @@
       <c r="A45" s="1">
         <v>42948</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>8.1364303428770393E-2</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>3316614698987.52</v>
       </c>
       <c r="D45" s="6">
@@ -10889,10 +11087,10 @@
       <c r="A46" s="1">
         <v>42979</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>8.33899076334879E-2</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>3418320243221.98</v>
       </c>
       <c r="D46" s="6">
@@ -10906,10 +11104,10 @@
       <c r="A47" s="1">
         <v>43009</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <v>8.0551882320272994E-2</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>3316485993738.0801</v>
       </c>
       <c r="D47" s="6">
@@ -10923,10 +11121,10 @@
       <c r="A48" s="1">
         <v>43040</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <v>8.4444640845001695E-2</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <v>3488304195807.98</v>
       </c>
       <c r="D48" s="6">
@@ -10940,10 +11138,10 @@
       <c r="A49" s="1">
         <v>43070</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <v>7.6664578823323101E-2</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>3149391054163.0898</v>
       </c>
       <c r="D49" s="6">
@@ -10957,10 +11155,10 @@
       <c r="A50" s="1">
         <v>43101</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <v>7.4383887148089703E-2</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>3056175243164.7798</v>
       </c>
       <c r="D50" s="6">
@@ -10974,10 +11172,10 @@
       <c r="A51" s="1">
         <v>43132</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <v>7.7104289683624094E-2</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>3214246926173.46</v>
       </c>
       <c r="D51" s="6">
@@ -10991,10 +11189,10 @@
       <c r="A52" s="1">
         <v>43160</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <v>8.5477918294292493E-2</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>3574033580947.23</v>
       </c>
       <c r="D52" s="6">
@@ -11008,10 +11206,10 @@
       <c r="A53" s="1">
         <v>43191</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <v>7.9499770921021395E-2</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>3343860411845.3501</v>
       </c>
       <c r="D53" s="6">
@@ -11025,10 +11223,10 @@
       <c r="A54" s="1">
         <v>43221</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <v>8.6631248166371799E-2</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>3662309113427.8301</v>
       </c>
       <c r="D54" s="6">
@@ -11042,10 +11240,10 @@
       <c r="A55" s="1">
         <v>43252</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <v>8.5333798544453804E-2</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>3626520721586.2002</v>
       </c>
       <c r="D55" s="6">
@@ -11059,10 +11257,10 @@
       <c r="A56" s="1">
         <v>43282</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <v>8.2098658168659605E-2</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>3507070535185.0498</v>
       </c>
       <c r="D56" s="6">
@@ -11076,10 +11274,10 @@
       <c r="A57" s="1">
         <v>43313</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <v>8.0332637074356394E-2</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>3430372219710.8799</v>
       </c>
       <c r="D57" s="6">
@@ -11093,10 +11291,10 @@
       <c r="A58" s="1">
         <v>43344</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <v>8.2500606503414703E-2</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>3550311427302.1802</v>
       </c>
       <c r="D58" s="6">
@@ -11110,10 +11308,10 @@
       <c r="A59" s="1">
         <v>43374</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <v>8.0242410198488004E-2</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>3454101720068.8599</v>
       </c>
       <c r="D59" s="6">
@@ -11127,10 +11325,10 @@
       <c r="A60" s="1">
         <v>43405</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <v>8.2801488634662801E-2</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="10">
         <v>3591458308489.3701</v>
       </c>
       <c r="D60" s="6">
@@ -11144,10 +11342,10 @@
       <c r="A61" s="1">
         <v>43435</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <v>8.0168582093159302E-2</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>3460880566115.48</v>
       </c>
       <c r="D61" s="6">
@@ -11161,10 +11359,10 @@
       <c r="A62" s="1">
         <v>43466</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="9">
         <v>7.1178873503671899E-2</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="10">
         <v>3179280591648.8799</v>
       </c>
       <c r="D62" s="6">
@@ -11178,10 +11376,10 @@
       <c r="A63" s="1">
         <v>43497</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <v>7.9527132244573306E-2</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>3612511589726.6201</v>
       </c>
       <c r="D63" s="6">
@@ -11195,10 +11393,10 @@
       <c r="A64" s="1">
         <v>43525</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="9">
         <v>8.0658009323824997E-2</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <v>3710466305626.0298</v>
       </c>
       <c r="D64" s="6">
@@ -11212,10 +11410,10 @@
       <c r="A65" s="1">
         <v>43556</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>7.8634153727876396E-2</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>3629908383974.27</v>
       </c>
       <c r="D65" s="6">
@@ -11229,10 +11427,10 @@
       <c r="A66" s="1">
         <v>43586</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <v>7.5294273315212504E-2</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="10">
         <v>3492883752581.4199</v>
       </c>
       <c r="D66" s="6">
@@ -11246,10 +11444,10 @@
       <c r="A67" s="1">
         <v>43617</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>8.2762754612575207E-2</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>3862454596400.6201</v>
       </c>
       <c r="D67" s="6">
@@ -11263,10 +11461,10 @@
       <c r="A68" s="1">
         <v>43647</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <v>8.0404843542681501E-2</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <v>3778213205968.6001</v>
       </c>
       <c r="D68" s="6">
@@ -11280,10 +11478,10 @@
       <c r="A69" s="1">
         <v>43678</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>8.1606170938207198E-2</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>3844247290342.6699</v>
       </c>
       <c r="D69" s="6">
@@ -11297,10 +11495,10 @@
       <c r="A70" s="1">
         <v>43709</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="9">
         <v>8.7917533128395994E-2</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="10">
         <v>4164719593399.98</v>
       </c>
       <c r="D70" s="6">
@@ -11314,10 +11512,10 @@
       <c r="A71" s="1">
         <v>43739</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="9">
         <v>8.2077169465330696E-2</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>3893460763593.3198</v>
       </c>
       <c r="D71" s="6">
@@ -11331,10 +11529,10 @@
       <c r="A72" s="1">
         <v>43770</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="9">
         <v>8.5528379899100199E-2</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="10">
         <v>4071594951902.4702</v>
       </c>
       <c r="D72" s="6">
@@ -11348,10 +11546,10 @@
       <c r="A73" s="1">
         <v>43800</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="9">
         <v>8.1098994958556894E-2</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>3847651471195.9102</v>
       </c>
       <c r="D73" s="6">
@@ -11365,10 +11563,10 @@
       <c r="A74" s="1">
         <v>43831</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="9">
         <v>8.2106436577667696E-2</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <v>4041609874426.6699</v>
       </c>
       <c r="D74" s="6">
@@ -11382,10 +11580,10 @@
       <c r="A75" s="1">
         <v>43862</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <v>7.53895999756512E-2</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>3769879156647.3901</v>
       </c>
       <c r="D75" s="6">
@@ -11399,10 +11597,10 @@
       <c r="A76" s="1">
         <v>43891</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>8.6147638550033906E-2</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <v>4375824530074.5601</v>
       </c>
       <c r="D76" s="6">
@@ -11416,10 +11614,10 @@
       <c r="A77" s="1">
         <v>43922</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <v>8.1943369223122994E-2</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>4282390284373.5898</v>
       </c>
       <c r="D77" s="6">
@@ -11433,10 +11631,10 @@
       <c r="A78" s="1">
         <v>43952</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="9">
         <v>8.3363548533069098E-2</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="10">
         <v>4412865641139.3496</v>
       </c>
       <c r="D78" s="6">
@@ -11450,10 +11648,10 @@
       <c r="A79" s="1">
         <v>43983</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="9">
         <v>9.3675607317217705E-2</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>4990834135615.6504</v>
       </c>
       <c r="D79" s="6">
@@ -11467,10 +11665,10 @@
       <c r="A80" s="1">
         <v>44013</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="9">
         <v>8.4602376016450306E-2</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="10">
         <v>4519929090275.5703</v>
       </c>
       <c r="D80" s="6">
@@ -11484,10 +11682,10 @@
       <c r="A81" s="1">
         <v>44044</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="9">
         <v>8.0635925146536197E-2</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>4478074627529.4297</v>
       </c>
       <c r="D81" s="6">
@@ -11501,10 +11699,10 @@
       <c r="A82" s="1">
         <v>44075</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="9">
         <v>8.0217949523078494E-2</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="10">
         <v>4478849771111.0898</v>
       </c>
       <c r="D82" s="6">
@@ -11518,10 +11716,10 @@
       <c r="A83" s="1">
         <v>44105</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="9">
         <v>8.5832351580255206E-2</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>4807408468661.3896</v>
       </c>
       <c r="D83" s="6">
@@ -11535,10 +11733,10 @@
       <c r="A84" s="1">
         <v>44136</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="9">
         <v>8.9952813019809202E-2</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="10">
         <v>5057471954009.1904</v>
       </c>
       <c r="D84" s="6">
@@ -11552,10 +11750,10 @@
       <c r="A85" s="1">
         <v>44166</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="9">
         <v>7.6293634208737707E-2</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>4270808765760.9902</v>
       </c>
       <c r="D85" s="6">
@@ -11569,10 +11767,10 @@
       <c r="A86" s="1">
         <v>44197</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="9">
         <v>8.6982048381505694E-2</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <v>4588298613727.29</v>
       </c>
       <c r="D86" s="6">
@@ -11586,10 +11784,10 @@
       <c r="A87" s="1">
         <v>44228</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="9">
         <v>8.5261534147713106E-2</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>4547613814170.9902</v>
       </c>
       <c r="D87" s="6">
@@ -11603,10 +11801,10 @@
       <c r="A88" s="1">
         <v>44256</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="9">
         <v>8.0145828445922607E-2</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <v>4304928150557.46</v>
       </c>
       <c r="D88" s="6">
@@ -11620,10 +11818,10 @@
       <c r="A89" s="1">
         <v>44287</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="9">
         <v>8.9606001028428098E-2</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>4864130575345.2402</v>
       </c>
       <c r="D89" s="6">
@@ -11637,10 +11835,10 @@
       <c r="A90" s="1">
         <v>44317</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="9">
         <v>8.4869337265318895E-2</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <v>4645632815551.2598</v>
       </c>
       <c r="D90" s="6">
@@ -11654,10 +11852,10 @@
       <c r="A91" s="1">
         <v>44348</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="9">
         <v>8.0385616175448593E-2</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>4424704296848.21</v>
       </c>
       <c r="D91" s="6">
@@ -11671,10 +11869,10 @@
       <c r="A92" s="1">
         <v>44378</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="9">
         <v>8.8776465354854603E-2</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>5012733487828.5098</v>
       </c>
       <c r="D92" s="6">
@@ -11688,10 +11886,10 @@
       <c r="A93" s="1">
         <v>44409</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="9">
         <v>0.103987916775138</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>5957590519161.7695</v>
       </c>
       <c r="D93" s="6">
@@ -11705,10 +11903,10 @@
       <c r="A94" s="1">
         <v>44440</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="9">
         <v>8.2986367835423194E-2</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <v>4777053840733.8301</v>
       </c>
       <c r="D94" s="6">
@@ -11722,10 +11920,10 @@
       <c r="A95" s="1">
         <v>44470</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="9">
         <v>8.4822745783669801E-2</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>5048530997245.5703</v>
       </c>
       <c r="D95" s="6">
@@ -11739,10 +11937,10 @@
       <c r="A96" s="1">
         <v>44501</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="9">
         <v>8.0467941748662106E-2</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <v>4803039292216.1299</v>
       </c>
       <c r="D96" s="6">
@@ -11756,10 +11954,10 @@
       <c r="A97" s="1">
         <v>44531</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="9">
         <v>8.4313324922136196E-2</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>5077476853939.9902</v>
       </c>
       <c r="D97" s="6">
@@ -11773,10 +11971,10 @@
       <c r="A98" s="1">
         <v>44562</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="9">
         <v>8.3900326855059201E-2</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="10">
         <v>4902344074291.7305</v>
       </c>
       <c r="D98" s="6">
@@ -11790,10 +11988,10 @@
       <c r="A99" s="1">
         <v>44593</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="9">
         <v>8.2814986869446702E-2</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>4889984302548.3604</v>
       </c>
       <c r="D99" s="6">
@@ -11807,10 +12005,10 @@
       <c r="A100" s="1">
         <v>44621</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="9">
         <v>9.2095894696996902E-2</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <v>5472900069208.1396</v>
       </c>
       <c r="D100" s="6">
@@ -11824,10 +12022,10 @@
       <c r="A101" s="1">
         <v>44652</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="9">
         <v>9.6089410101591E-2</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>5828521786505.7002</v>
       </c>
       <c r="D101" s="6">
@@ -11841,10 +12039,10 @@
       <c r="A102" s="1">
         <v>44682</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="9">
         <v>8.4365374426336806E-2</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="10">
         <v>5214724518150.04</v>
       </c>
       <c r="D102" s="6">
@@ -11858,10 +12056,10 @@
       <c r="A103" s="1">
         <v>44713</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="9">
         <v>8.7244698622566702E-2</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>5466097611269.7598</v>
       </c>
       <c r="D103" s="6">
@@ -11875,10 +12073,10 @@
       <c r="A104" s="1">
         <v>44743</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="9">
         <v>9.5643971008620404E-2</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="10">
         <v>6171823302733.21</v>
       </c>
       <c r="D104" s="6">
@@ -11892,10 +12090,10 @@
       <c r="A105" s="1">
         <v>44774</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="9">
         <v>8.4882039139785107E-2</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>5496249877890.6602</v>
       </c>
       <c r="D105" s="6">
@@ -11909,10 +12107,10 @@
       <c r="A106" s="1">
         <v>44805</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="9">
         <v>8.6881273282872401E-2</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="10">
         <v>5701184560167.6904</v>
       </c>
       <c r="D106" s="6">
@@ -11926,10 +12124,10 @@
       <c r="A107" s="1">
         <v>44835</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="9">
         <v>8.7062092871059996E-2</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>5783137459807.3301</v>
       </c>
       <c r="D107" s="6">
@@ -11943,10 +12141,10 @@
       <c r="A108" s="1">
         <v>44866</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="9">
         <v>8.66658018223707E-2</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <v>5848575534289.2598</v>
       </c>
       <c r="D108" s="6">
@@ -11960,10 +12158,10 @@
       <c r="A109" s="1">
         <v>44896</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="9">
         <v>9.5273158671379699E-2</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>6807349406388.5303</v>
       </c>
       <c r="D109" s="6">
@@ -11977,10 +12175,10 @@
       <c r="A110" s="1">
         <v>44927</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="9">
         <v>9.3285794837066699E-2</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <v>6451919769075.7695</v>
       </c>
       <c r="D110" s="6">
@@ -11994,10 +12192,10 @@
       <c r="A111" s="1">
         <v>44958</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="9">
         <v>8.7860510244941195E-2</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>6155994000636.3301</v>
       </c>
       <c r="D111" s="6">
@@ -12011,10 +12209,10 @@
       <c r="A112" s="1">
         <v>44986</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="9">
         <v>7.8855675906151695E-2</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <v>5593345909859.4805</v>
       </c>
       <c r="D112" s="6">
@@ -12028,10 +12226,10 @@
       <c r="A113" s="1">
         <v>45017</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="9">
         <v>8.5490137262282495E-2</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>6071178363432.6504</v>
       </c>
       <c r="D113" s="6">
@@ -12045,10 +12243,10 @@
       <c r="A114" s="1">
         <v>45047</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="9">
         <v>9.0517139213684997E-2</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="10">
         <v>6447432144013.2002</v>
       </c>
       <c r="D114" s="6">
@@ -12062,10 +12260,10 @@
       <c r="A115" s="1">
         <v>45078</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="9">
         <v>8.1399250157654202E-2</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>5879554868228.6797</v>
       </c>
       <c r="D115" s="6">
@@ -12079,10 +12277,10 @@
       <c r="A116" s="1">
         <v>45108</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="9">
         <v>8.3201544521322807E-2</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="10">
         <v>5999630070010.04</v>
       </c>
       <c r="D116" s="6">
@@ -12096,10 +12294,10 @@
       <c r="A117" s="1">
         <v>45139</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="9">
         <v>8.1149193717019896E-2</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>5863688693067.0801</v>
       </c>
       <c r="D117" s="6">
@@ -12113,10 +12311,10 @@
       <c r="A118" s="1">
         <v>45170</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="9">
         <v>8.8597394820468703E-2</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <v>6517037711379.96</v>
       </c>
       <c r="D118" s="6">
@@ -12130,10 +12328,10 @@
       <c r="A119" s="1">
         <v>45200</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="9">
         <v>8.3961386675261498E-2</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>6322781914601.6396</v>
       </c>
       <c r="D119" s="6">
@@ -12147,10 +12345,10 @@
       <c r="A120" s="1">
         <v>45231</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="9">
         <v>8.5228884661221693E-2</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="10">
         <v>6453154068452.7402</v>
       </c>
       <c r="D120" s="6">
@@ -12164,10 +12362,10 @@
       <c r="A121" s="1">
         <v>45261</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="9">
         <v>9.1074203525746494E-2</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>7007036509396.5596</v>
       </c>
       <c r="D121" s="6">
@@ -12181,10 +12379,10 @@
       <c r="A122" s="1">
         <v>45292</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="9">
         <v>7.5616616895576694E-2</v>
       </c>
-      <c r="C122" s="11">
+      <c r="C122" s="10">
         <v>6246356248077</v>
       </c>
       <c r="D122" s="6">
@@ -12198,10 +12396,10 @@
       <c r="A123" s="1">
         <v>45323</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="9">
         <v>8.9780723172706398E-2</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <v>7497572280869.6201</v>
       </c>
       <c r="D123" s="6">
@@ -12215,10 +12413,10 @@
       <c r="A124" s="1">
         <v>45352</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="9">
         <v>8.11855057101869E-2</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="10">
         <v>6870803947230.4404</v>
       </c>
       <c r="D124" s="6">
@@ -12232,10 +12430,10 @@
       <c r="A125" s="1">
         <v>45383</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="9">
         <v>8.0754984822188805E-2</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>6816728183431.6797</v>
       </c>
       <c r="D125" s="6">
@@ -12249,10 +12447,10 @@
       <c r="A126" s="1">
         <v>45413</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="9">
         <v>8.5157455807396198E-2</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="10">
         <v>7219509619482.46</v>
       </c>
       <c r="D126" s="6">
@@ -12266,10 +12464,10 @@
       <c r="A127" s="1">
         <v>45444</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="9">
         <v>8.5101471077041801E-2</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>7314732318588.4004</v>
       </c>
       <c r="D127" s="6">
@@ -12283,10 +12481,10 @@
       <c r="A128" s="1">
         <v>45474</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="9">
         <v>7.9508405070431998E-2</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="10">
         <v>6844149900510.7803</v>
       </c>
       <c r="D128" s="6">
@@ -12300,10 +12498,10 @@
       <c r="A129" s="1">
         <v>45505</v>
       </c>
-      <c r="B129" s="10">
+      <c r="B129" s="9">
         <v>7.8077882617626604E-2</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>6757964683623.4297</v>
       </c>
       <c r="D129" s="6">
@@ -12317,10 +12515,10 @@
       <c r="A130" s="1">
         <v>45536</v>
       </c>
-      <c r="B130" s="10">
+      <c r="B130" s="9">
         <v>8.7595292378169307E-2</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="10">
         <v>7683030870066.2002</v>
       </c>
       <c r="D130" s="6">
@@ -12334,10 +12532,10 @@
       <c r="A131" s="1">
         <v>45566</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="9">
         <v>9.0402448621115503E-2</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>7925026761820.0703</v>
       </c>
       <c r="D131" s="6">
@@ -12351,10 +12549,10 @@
       <c r="A132" s="1">
         <v>45597</v>
       </c>
-      <c r="B132" s="10">
+      <c r="B132" s="9">
         <v>8.7605457417919905E-2</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="10">
         <v>7848959214068.7695</v>
       </c>
       <c r="D132" s="6">
@@ -12368,10 +12566,10 @@
       <c r="A133" s="1">
         <v>45627</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="9">
         <v>9.1657743398141298E-2</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>8338102826680.1699</v>
       </c>
       <c r="D133" s="6">
@@ -12385,10 +12583,10 @@
       <c r="A134" s="1">
         <v>45658</v>
       </c>
-      <c r="B134" s="10">
+      <c r="B134" s="9">
         <v>9.5265747161119907E-2</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="10">
         <v>8852480350273.5098</v>
       </c>
       <c r="D134" s="6">
@@ -12402,10 +12600,10 @@
       <c r="A135" s="1">
         <v>45689</v>
       </c>
-      <c r="B135" s="10">
+      <c r="B135" s="9">
         <v>8.9493682975044897E-2</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>8407643806193.8096</v>
       </c>
       <c r="D135" s="6">
@@ -12419,10 +12617,10 @@
       <c r="A136" s="1">
         <v>45717</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="9">
         <v>8.2605180837207207E-2</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="10">
         <v>7790663108058.9199</v>
       </c>
       <c r="D136" s="6">
@@ -12436,10 +12634,10 @@
       <c r="A137" s="1">
         <v>45748</v>
       </c>
-      <c r="B137" s="10">
+      <c r="B137" s="9">
         <v>8.7523705241935201E-2</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>8278564738437.8096</v>
       </c>
       <c r="D137" s="6">
@@ -12453,10 +12651,10 @@
       <c r="A138" s="1">
         <v>45778</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="9">
         <v>8.2150783392493001E-2</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="10">
         <v>7819094354271.9697</v>
       </c>
       <c r="D138" s="6">
@@ -12470,10 +12668,10 @@
       <c r="A139" s="1">
         <v>45809</v>
       </c>
-      <c r="B139" s="10">
+      <c r="B139" s="9">
         <v>8.4867935529706395E-2</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>8182743961262.0498</v>
       </c>
       <c r="D139" s="6">
@@ -12487,10 +12685,10 @@
       <c r="A140" s="1">
         <v>45839</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="9">
         <v>9.0124981281222302E-2</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="10">
         <v>8723612948668.8398</v>
       </c>
       <c r="D140" s="6">
@@ -12498,6 +12696,2505 @@
       </c>
       <c r="E140" s="6">
         <v>50042377715175.797</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E146"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>41640</v>
+      </c>
+      <c r="B2" s="9">
+        <v>5.8379585845818802E-2</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1894711442286.8601</v>
+      </c>
+      <c r="D2" s="6">
+        <v>32207717768137.199</v>
+      </c>
+      <c r="E2" s="6">
+        <v>11435376960672.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
+        <v>41671</v>
+      </c>
+      <c r="B3" s="9">
+        <v>9.5673784018701302E-2</v>
+      </c>
+      <c r="C3" s="10">
+        <v>3128285858718.77</v>
+      </c>
+      <c r="D3" s="6">
+        <v>32448815966308.102</v>
+      </c>
+      <c r="E3" s="6">
+        <v>15598774764239.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>41699</v>
+      </c>
+      <c r="B4" s="9">
+        <v>7.9333809387746507E-2</v>
+      </c>
+      <c r="C4" s="10">
+        <v>2608198324025.8398</v>
+      </c>
+      <c r="D4" s="6">
+        <v>32676232019173.102</v>
+      </c>
+      <c r="E4" s="6">
+        <v>15763245876095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>41730</v>
+      </c>
+      <c r="B5" s="9">
+        <v>7.8661190290802693E-2</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2612561563700.98</v>
+      </c>
+      <c r="D5" s="6">
+        <v>32936396427888.5</v>
+      </c>
+      <c r="E5" s="6">
+        <v>15747330590369.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>41760</v>
+      </c>
+      <c r="B6" s="9">
+        <v>8.0384445414080297E-2</v>
+      </c>
+      <c r="C6" s="10">
+        <v>2691649521863.6001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>33157733689330.699</v>
+      </c>
+      <c r="E6" s="6">
+        <v>15856625808011.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>41791</v>
+      </c>
+      <c r="B7" s="9">
+        <v>8.0209605641749601E-2</v>
+      </c>
+      <c r="C7" s="10">
+        <v>2698202272680.0498</v>
+      </c>
+      <c r="D7" s="6">
+        <v>33397265336829.898</v>
+      </c>
+      <c r="E7" s="6">
+        <v>15912826007103.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
+        <v>41821</v>
+      </c>
+      <c r="B8" s="9">
+        <v>8.0184396144570402E-2</v>
+      </c>
+      <c r="C8" s="10">
+        <v>2701399662792.2002</v>
+      </c>
+      <c r="D8" s="6">
+        <v>33643513970584.801</v>
+      </c>
+      <c r="E8" s="6">
+        <v>15944574640514.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
+        <v>41852</v>
+      </c>
+      <c r="B9" s="9">
+        <v>8.3254926824489595E-2</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2819508388619.8701</v>
+      </c>
+      <c r="D9" s="6">
+        <v>33888808428472.898</v>
+      </c>
+      <c r="E9" s="6">
+        <v>15993082798215.801</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
+        <v>41883</v>
+      </c>
+      <c r="B10" s="9">
+        <v>8.25789127991991E-2</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2808834979206.4199</v>
+      </c>
+      <c r="D10" s="6">
+        <v>34139625735598.602</v>
+      </c>
+      <c r="E10" s="6">
+        <v>16047821306952.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1">
+        <v>41913</v>
+      </c>
+      <c r="B11" s="9">
+        <v>8.6760275972860595E-2</v>
+      </c>
+      <c r="C11" s="10">
+        <v>2954939525984.48</v>
+      </c>
+      <c r="D11" s="6">
+        <v>34383952710074.801</v>
+      </c>
+      <c r="E11" s="6">
+        <v>16104368499859.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1">
+        <v>41944</v>
+      </c>
+      <c r="B12" s="9">
+        <v>7.8259227591225694E-2</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2674844822075.2598</v>
+      </c>
+      <c r="D12" s="6">
+        <v>34578180939684.602</v>
+      </c>
+      <c r="E12" s="6">
+        <v>16082548480227.199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1">
+        <v>41974</v>
+      </c>
+      <c r="B13" s="9">
+        <v>8.9026259460649501E-2</v>
+      </c>
+      <c r="C13" s="10">
+        <v>3106813925878.8101</v>
+      </c>
+      <c r="D13" s="6">
+        <v>35621573242105.203</v>
+      </c>
+      <c r="E13" s="6">
+        <v>16167298390715.301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1">
+        <v>42005</v>
+      </c>
+      <c r="B14" s="9">
+        <v>9.0507669567015794E-2</v>
+      </c>
+      <c r="C14" s="10">
+        <v>3278632431601.3799</v>
+      </c>
+      <c r="D14" s="6">
+        <v>35876314218636.398</v>
+      </c>
+      <c r="E14" s="6">
+        <v>19103780733584.398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B15" s="9">
+        <v>8.6799714054401803E-2</v>
+      </c>
+      <c r="C15" s="10">
+        <v>3161181150358.2202</v>
+      </c>
+      <c r="D15" s="6">
+        <v>36117539255911.898</v>
+      </c>
+      <c r="E15" s="6">
+        <v>19051322862840.602</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B16" s="9">
+        <v>7.7315267178091604E-2</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2830137827129.6899</v>
+      </c>
+      <c r="D16" s="6">
+        <v>36397596453769</v>
+      </c>
+      <c r="E16" s="6">
+        <v>18735031733633.398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1">
+        <v>42095</v>
+      </c>
+      <c r="B17" s="9">
+        <v>8.9044827877414107E-2</v>
+      </c>
+      <c r="C17" s="10">
+        <v>3245706624114.2402</v>
+      </c>
+      <c r="D17" s="6">
+        <v>36200432596499.898</v>
+      </c>
+      <c r="E17" s="6">
+        <v>18889589234857.801</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1">
+        <v>42125</v>
+      </c>
+      <c r="B18" s="9">
+        <v>8.0558665294347603E-2</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2968887567441.9502</v>
+      </c>
+      <c r="D18" s="6">
+        <v>36492245392292.398</v>
+      </c>
+      <c r="E18" s="6">
+        <v>18681276125122.898</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1">
+        <v>42156</v>
+      </c>
+      <c r="B19" s="9">
+        <v>8.0074392495774596E-2</v>
+      </c>
+      <c r="C19" s="10">
+        <v>2958793381734.0801</v>
+      </c>
+      <c r="D19" s="6">
+        <v>36743466524042.797</v>
+      </c>
+      <c r="E19" s="6">
+        <v>18580056399351.301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1">
+        <v>42186</v>
+      </c>
+      <c r="B20" s="9">
+        <v>8.5388070674853198E-2</v>
+      </c>
+      <c r="C20" s="10">
+        <v>3160113936745.0698</v>
+      </c>
+      <c r="D20" s="6">
+        <v>37003228667441.203</v>
+      </c>
+      <c r="E20" s="6">
+        <v>18613044709063.102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1">
+        <v>42217</v>
+      </c>
+      <c r="B21" s="9">
+        <v>8.2629983744846106E-2</v>
+      </c>
+      <c r="C21" s="10">
+        <v>3072275607652.5</v>
+      </c>
+      <c r="D21" s="6">
+        <v>37246384832055.898</v>
+      </c>
+      <c r="E21" s="6">
+        <v>18499514971083.301</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1">
+        <v>42248</v>
+      </c>
+      <c r="B22" s="9">
+        <v>7.54576790116087E-2</v>
+      </c>
+      <c r="C22" s="10">
+        <v>2815732487166.0601</v>
+      </c>
+      <c r="D22" s="6">
+        <v>37511821436573.203</v>
+      </c>
+      <c r="E22" s="6">
+        <v>18383260089667.801</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1">
+        <v>42278</v>
+      </c>
+      <c r="B23" s="9">
+        <v>7.8923213612904497E-2</v>
+      </c>
+      <c r="C23" s="10">
+        <v>2954182895239.1099</v>
+      </c>
+      <c r="D23" s="6">
+        <v>37794242608566.398</v>
+      </c>
+      <c r="E23" s="6">
+        <v>18316138968078.602</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="1">
+        <v>42309</v>
+      </c>
+      <c r="B24" s="9">
+        <v>7.6992660250402106E-2</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2906999707649.1099</v>
+      </c>
+      <c r="D24" s="6">
+        <v>38096404362681.898</v>
+      </c>
+      <c r="E24" s="6">
+        <v>18294166301917.102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="1">
+        <v>42339</v>
+      </c>
+      <c r="B25" s="9">
+        <v>7.6440848379227599E-2</v>
+      </c>
+      <c r="C25" s="10">
+        <v>2877684099130.5098</v>
+      </c>
+      <c r="D25" s="6">
+        <v>38395914618113</v>
+      </c>
+      <c r="E25" s="6">
+        <v>18136363850939.301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="1">
+        <v>42370</v>
+      </c>
+      <c r="B26" s="9">
+        <v>6.2247149631624699E-2</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2305362140202.3999</v>
+      </c>
+      <c r="D26" s="6">
+        <v>36605716527808.297</v>
+      </c>
+      <c r="E26" s="6">
+        <v>13522288889410.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="1">
+        <v>42401</v>
+      </c>
+      <c r="B27" s="9">
+        <v>7.9258799469666505E-2</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2949817277237.3999</v>
+      </c>
+      <c r="D27" s="6">
+        <v>36843248724402.797</v>
+      </c>
+      <c r="E27" s="6">
+        <v>16193775466163.699</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="1">
+        <v>42430</v>
+      </c>
+      <c r="B28" s="9">
+        <v>9.4052911345863896E-2</v>
+      </c>
+      <c r="C28" s="10">
+        <v>3509748898726.3599</v>
+      </c>
+      <c r="D28" s="6">
+        <v>37085165850070.898</v>
+      </c>
+      <c r="E28" s="6">
+        <v>18207922051078.602</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B29" s="9">
+        <v>8.2028749563870795E-2</v>
+      </c>
+      <c r="C29" s="10">
+        <v>3086119953060.25</v>
+      </c>
+      <c r="D29" s="6">
+        <v>37361992075092.203</v>
+      </c>
+      <c r="E29" s="6">
+        <v>18271237279106.602</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="1">
+        <v>42491</v>
+      </c>
+      <c r="B30" s="9">
+        <v>8.5176958597164801E-2</v>
+      </c>
+      <c r="C30" s="10">
+        <v>3228527030434.7998</v>
+      </c>
+      <c r="D30" s="6">
+        <v>37648446598129.398</v>
+      </c>
+      <c r="E30" s="6">
+        <v>18338647483195.898</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="1">
+        <v>42522</v>
+      </c>
+      <c r="B31" s="9">
+        <v>8.3139409063477707E-2</v>
+      </c>
+      <c r="C31" s="10">
+        <v>3167369465083.3398</v>
+      </c>
+      <c r="D31" s="6">
+        <v>37960614021622.5</v>
+      </c>
+      <c r="E31" s="6">
+        <v>18446881553434.301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="1">
+        <v>42552</v>
+      </c>
+      <c r="B32" s="9">
+        <v>7.7859643266832895E-2</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2978313201706.5601</v>
+      </c>
+      <c r="D32" s="6">
+        <v>38170690975907.398</v>
+      </c>
+      <c r="E32" s="6">
+        <v>18415863584041.301</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="1">
+        <v>42583</v>
+      </c>
+      <c r="B33" s="9">
+        <v>8.3757933166193496E-2</v>
+      </c>
+      <c r="C33" s="10">
+        <v>3216349637309.8599</v>
+      </c>
+      <c r="D33" s="6">
+        <v>38524885645809.102</v>
+      </c>
+      <c r="E33" s="6">
+        <v>18533459878643.801</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="1">
+        <v>42614</v>
+      </c>
+      <c r="B34" s="9">
+        <v>8.3708991327487201E-2</v>
+      </c>
+      <c r="C34" s="10">
+        <v>3232823021064.7402</v>
+      </c>
+      <c r="D34" s="6">
+        <v>38826161759049.797</v>
+      </c>
+      <c r="E34" s="6">
+        <v>18649950223402.602</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="1">
+        <v>42644</v>
+      </c>
+      <c r="B35" s="9">
+        <v>7.9600288391895896E-2</v>
+      </c>
+      <c r="C35" s="10">
+        <v>3084832337562.0498</v>
+      </c>
+      <c r="D35" s="6">
+        <v>39082003504297.297</v>
+      </c>
+      <c r="E35" s="6">
+        <v>18692246082701.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="1">
+        <v>42675</v>
+      </c>
+      <c r="B36" s="9">
+        <v>8.2046986700456806E-2</v>
+      </c>
+      <c r="C36" s="10">
+        <v>3211927786385.04</v>
+      </c>
+      <c r="D36" s="6">
+        <v>39481294430224.203</v>
+      </c>
+      <c r="E36" s="6">
+        <v>18778496543572.898</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="1">
+        <v>42705</v>
+      </c>
+      <c r="B37" s="9">
+        <v>8.4380670594579807E-2</v>
+      </c>
+      <c r="C37" s="10">
+        <v>3280627283040.6699</v>
+      </c>
+      <c r="D37" s="6">
+        <v>39721711875317.703</v>
+      </c>
+      <c r="E37" s="6">
+        <v>18929382670498.602</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="1">
+        <v>42736</v>
+      </c>
+      <c r="B38" s="9">
+        <v>8.7692514574177705E-2</v>
+      </c>
+      <c r="C38" s="10">
+        <v>3413965655328.4399</v>
+      </c>
+      <c r="D38" s="6">
+        <v>38613026065500.5</v>
+      </c>
+      <c r="E38" s="6">
+        <v>20901024007897.199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="1">
+        <v>42767</v>
+      </c>
+      <c r="B39" s="9">
+        <v>7.6713296718701099E-2</v>
+      </c>
+      <c r="C39" s="10">
+        <v>3021486954041.1099</v>
+      </c>
+      <c r="D39" s="6">
+        <v>38945501216444.398</v>
+      </c>
+      <c r="E39" s="6">
+        <v>19201038344201.301</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="1">
+        <v>42795</v>
+      </c>
+      <c r="B40" s="9">
+        <v>8.7312216229452594E-2</v>
+      </c>
+      <c r="C40" s="10">
+        <v>3457575226847.8501</v>
+      </c>
+      <c r="D40" s="6">
+        <v>39296760835062.102</v>
+      </c>
+      <c r="E40" s="6">
+        <v>19422206865271.898</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="1">
+        <v>42826</v>
+      </c>
+      <c r="B41" s="9">
+        <v>7.62503059119988E-2</v>
+      </c>
+      <c r="C41" s="10">
+        <v>3044267610022.8301</v>
+      </c>
+      <c r="D41" s="6">
+        <v>39590784324130.5</v>
+      </c>
+      <c r="E41" s="6">
+        <v>19227168078306.898</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="1">
+        <v>42856</v>
+      </c>
+      <c r="B42" s="9">
+        <v>8.6109620048612306E-2</v>
+      </c>
+      <c r="C42" s="10">
+        <v>3449320471430.4102</v>
+      </c>
+      <c r="D42" s="6">
+        <v>39861572821152.898</v>
+      </c>
+      <c r="E42" s="6">
+        <v>19361877496373.301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="1">
+        <v>42887</v>
+      </c>
+      <c r="B43" s="9">
+        <v>8.0996293789181398E-2</v>
+      </c>
+      <c r="C43" s="10">
+        <v>3259998721264.2402</v>
+      </c>
+      <c r="D43" s="6">
+        <v>40152751742048.797</v>
+      </c>
+      <c r="E43" s="6">
+        <v>19385246751357.699</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="1">
+        <v>42917</v>
+      </c>
+      <c r="B44" s="9">
+        <v>7.8148877250122706E-2</v>
+      </c>
+      <c r="C44" s="10">
+        <v>3186560019573.1499</v>
+      </c>
+      <c r="D44" s="6">
+        <v>40591906653062.102</v>
+      </c>
+      <c r="E44" s="6">
+        <v>19421538608962.898</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="1">
+        <v>42948</v>
+      </c>
+      <c r="B45" s="9">
+        <v>8.1587514800539093E-2</v>
+      </c>
+      <c r="C45" s="10">
+        <v>3326035060368.1802</v>
+      </c>
+      <c r="D45" s="6">
+        <v>40847430978567.703</v>
+      </c>
+      <c r="E45" s="6">
+        <v>19481180039819</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B46" s="9">
+        <v>8.3674745049440696E-2</v>
+      </c>
+      <c r="C46" s="10">
+        <v>3429757321135.0698</v>
+      </c>
+      <c r="D46" s="6">
+        <v>41134659264148.297</v>
+      </c>
+      <c r="E46" s="6">
+        <v>19542223034606.398</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="1">
+        <v>43009</v>
+      </c>
+      <c r="B47" s="9">
+        <v>8.04403757790777E-2</v>
+      </c>
+      <c r="C47" s="10">
+        <v>3312390406164.6802</v>
+      </c>
+      <c r="D47" s="6">
+        <v>41495506714736.398</v>
+      </c>
+      <c r="E47" s="6">
+        <v>19598894116891.102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="1">
+        <v>43040</v>
+      </c>
+      <c r="B48" s="9">
+        <v>8.4291083899996497E-2</v>
+      </c>
+      <c r="C48" s="10">
+        <v>3483624902402.77</v>
+      </c>
+      <c r="D48" s="6">
+        <v>41707412699629.797</v>
+      </c>
+      <c r="E48" s="6">
+        <v>19685755985160.699</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="1">
+        <v>43070</v>
+      </c>
+      <c r="B49" s="9">
+        <v>7.7399530987007595E-2</v>
+      </c>
+      <c r="C49" s="10">
+        <v>3181773292117.98</v>
+      </c>
+      <c r="D49" s="6">
+        <v>42020896387810.602</v>
+      </c>
+      <c r="E49" s="6">
+        <v>19671936933787.398</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="1">
+        <v>43101</v>
+      </c>
+      <c r="B50" s="9">
+        <v>7.3904342084978397E-2</v>
+      </c>
+      <c r="C50" s="10">
+        <v>3039319910139.25</v>
+      </c>
+      <c r="D50" s="6">
+        <v>40869111344427.898</v>
+      </c>
+      <c r="E50" s="6">
+        <v>19712876936869.199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="1">
+        <v>43132</v>
+      </c>
+      <c r="B51" s="9">
+        <v>7.6916518776938295E-2</v>
+      </c>
+      <c r="C51" s="10">
+        <v>3206145945294.2598</v>
+      </c>
+      <c r="D51" s="6">
+        <v>41166024240614.398</v>
+      </c>
+      <c r="E51" s="6">
+        <v>19580780366027.699</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="1">
+        <v>43160</v>
+      </c>
+      <c r="B52" s="9">
+        <v>8.5231660155362904E-2</v>
+      </c>
+      <c r="C52" s="10">
+        <v>3562951982540.3398</v>
+      </c>
+      <c r="D52" s="6">
+        <v>41365227105041.398</v>
+      </c>
+      <c r="E52" s="6">
+        <v>19797919592714.398</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="1">
+        <v>43191</v>
+      </c>
+      <c r="B53" s="9">
+        <v>7.9192271753202204E-2</v>
+      </c>
+      <c r="C53" s="10">
+        <v>3329325065602.02</v>
+      </c>
+      <c r="D53" s="6">
+        <v>41673980500301.797</v>
+      </c>
+      <c r="E53" s="6">
+        <v>19881644436694.102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="1">
+        <v>43221</v>
+      </c>
+      <c r="B54" s="9">
+        <v>8.6523185535569605E-2</v>
+      </c>
+      <c r="C54" s="10">
+        <v>3656720889204.98</v>
+      </c>
+      <c r="D54" s="6">
+        <v>42009586298309.102</v>
+      </c>
+      <c r="E54" s="6">
+        <v>20038961664556.398</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="1">
+        <v>43252</v>
+      </c>
+      <c r="B55" s="9">
+        <v>8.4964781897841193E-2</v>
+      </c>
+      <c r="C55" s="10">
+        <v>3607476253590.1499</v>
+      </c>
+      <c r="D55" s="6">
+        <v>42324398003005.5</v>
+      </c>
+      <c r="E55" s="6">
+        <v>20135004074333.301</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="1">
+        <v>43282</v>
+      </c>
+      <c r="B56" s="9">
+        <v>8.1771641244115303E-2</v>
+      </c>
+      <c r="C56" s="10">
+        <v>3489090390707.7798</v>
+      </c>
+      <c r="D56" s="6">
+        <v>42545322170399.898</v>
+      </c>
+      <c r="E56" s="6">
+        <v>20228954016601.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="1">
+        <v>43313</v>
+      </c>
+      <c r="B57" s="9">
+        <v>8.0553067835532705E-2</v>
+      </c>
+      <c r="C57" s="10">
+        <v>3440117210632.75</v>
+      </c>
+      <c r="D57" s="6">
+        <v>42872373129613.797</v>
+      </c>
+      <c r="E57" s="6">
+        <v>20314059717593.398</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="1">
+        <v>43344</v>
+      </c>
+      <c r="B58" s="9">
+        <v>8.2593650535471894E-2</v>
+      </c>
+      <c r="C58" s="10">
+        <v>3552921922857.2202</v>
+      </c>
+      <c r="D58" s="6">
+        <v>43201322037794.203</v>
+      </c>
+      <c r="E58" s="6">
+        <v>20346695702021.301</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="1">
+        <v>43374</v>
+      </c>
+      <c r="B59" s="9">
+        <v>8.0314654923303197E-2</v>
+      </c>
+      <c r="C59" s="10">
+        <v>3458843481933.0298</v>
+      </c>
+      <c r="D59" s="6">
+        <v>43507465112023.797</v>
+      </c>
+      <c r="E59" s="6">
+        <v>20454403157952.699</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="1">
+        <v>43405</v>
+      </c>
+      <c r="B60" s="9">
+        <v>8.2650840807729997E-2</v>
+      </c>
+      <c r="C60" s="10">
+        <v>3586636947506.9902</v>
+      </c>
+      <c r="D60" s="6">
+        <v>43922274401290.297</v>
+      </c>
+      <c r="E60" s="6">
+        <v>20547004077784.199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="1">
+        <v>43435</v>
+      </c>
+      <c r="B61" s="9">
+        <v>8.0937570274055806E-2</v>
+      </c>
+      <c r="C61" s="10">
+        <v>3496486610305.2402</v>
+      </c>
+      <c r="D61" s="6">
+        <v>44225606094950.203</v>
+      </c>
+      <c r="E61" s="6">
+        <v>20705063761060.699</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="1">
+        <v>43466</v>
+      </c>
+      <c r="B62" s="9">
+        <v>7.0719850284686997E-2</v>
+      </c>
+      <c r="C62" s="10">
+        <v>3161735370855.29</v>
+      </c>
+      <c r="D62" s="6">
+        <v>44529884423917.703</v>
+      </c>
+      <c r="E62" s="6">
+        <v>20567376382610.699</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="1">
+        <v>43497</v>
+      </c>
+      <c r="B63" s="9">
+        <v>7.9333401279531895E-2</v>
+      </c>
+      <c r="C63" s="10">
+        <v>3603407779099.9199</v>
+      </c>
+      <c r="D63" s="6">
+        <v>44920978262795</v>
+      </c>
+      <c r="E63" s="6">
+        <v>20937970657143.898</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="1">
+        <v>43525</v>
+      </c>
+      <c r="B64" s="9">
+        <v>8.0241989695840593E-2</v>
+      </c>
+      <c r="C64" s="10">
+        <v>3689327280668.2998</v>
+      </c>
+      <c r="D64" s="6">
+        <v>45302491859668.102</v>
+      </c>
+      <c r="E64" s="6">
+        <v>20843850869548.398</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="1">
+        <v>43556</v>
+      </c>
+      <c r="B65" s="9">
+        <v>7.85091129979619E-2</v>
+      </c>
+      <c r="C65" s="10">
+        <v>3623563009723.1001</v>
+      </c>
+      <c r="D65" s="6">
+        <v>45694374509986.203</v>
+      </c>
+      <c r="E65" s="6">
+        <v>21117061995179.898</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="1">
+        <v>43586</v>
+      </c>
+      <c r="B66" s="9">
+        <v>7.5200271616245901E-2</v>
+      </c>
+      <c r="C66" s="10">
+        <v>3487548936297.73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>45997535670123.898</v>
+      </c>
+      <c r="E66" s="6">
+        <v>21209871923098</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="1">
+        <v>43617</v>
+      </c>
+      <c r="B67" s="9">
+        <v>8.2216672944747493E-2</v>
+      </c>
+      <c r="C67" s="10">
+        <v>3832160253518.54</v>
+      </c>
+      <c r="D67" s="6">
+        <v>46309243364341.203</v>
+      </c>
+      <c r="E67" s="6">
+        <v>21294219935331.301</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="1">
+        <v>43647</v>
+      </c>
+      <c r="B68" s="9">
+        <v>8.0267677665860696E-2</v>
+      </c>
+      <c r="C68" s="10">
+        <v>3768649957336.98</v>
+      </c>
+      <c r="D68" s="6">
+        <v>46814306243937.703</v>
+      </c>
+      <c r="E68" s="6">
+        <v>21558266164652.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="1">
+        <v>43678</v>
+      </c>
+      <c r="B69" s="9">
+        <v>8.1643388481838802E-2</v>
+      </c>
+      <c r="C69" s="10">
+        <v>3845131768226.25</v>
+      </c>
+      <c r="D69" s="6">
+        <v>47137685804287.797</v>
+      </c>
+      <c r="E69" s="6">
+        <v>21798694277493.301</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="1">
+        <v>43709</v>
+      </c>
+      <c r="B70" s="9">
+        <v>8.8218300073862693E-2</v>
+      </c>
+      <c r="C70" s="10">
+        <v>4178676478240.8198</v>
+      </c>
+      <c r="D70" s="6">
+        <v>47518956664994.602</v>
+      </c>
+      <c r="E70" s="6">
+        <v>22124609455655.199</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="1">
+        <v>43739</v>
+      </c>
+      <c r="B71" s="9">
+        <v>8.2151074818905198E-2</v>
+      </c>
+      <c r="C71" s="10">
+        <v>3898806234482.4399</v>
+      </c>
+      <c r="D71" s="6">
+        <v>47938745500854</v>
+      </c>
+      <c r="E71" s="6">
+        <v>22389601934281.801</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="1">
+        <v>43770</v>
+      </c>
+      <c r="B72" s="9">
+        <v>8.5177806970677297E-2</v>
+      </c>
+      <c r="C72" s="10">
+        <v>4055535758603.1201</v>
+      </c>
+      <c r="D72" s="6">
+        <v>48273491158861.797</v>
+      </c>
+      <c r="E72" s="6">
+        <v>22648948979124</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="1">
+        <v>43800</v>
+      </c>
+      <c r="B73" s="9">
+        <v>8.2064771100441997E-2</v>
+      </c>
+      <c r="C73" s="10">
+        <v>3897413632014.52</v>
+      </c>
+      <c r="D73" s="6">
+        <v>48730595219502.703</v>
+      </c>
+      <c r="E73" s="6">
+        <v>22972163730756.102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="1">
+        <v>43831</v>
+      </c>
+      <c r="B74" s="9">
+        <v>8.1576737347532693E-2</v>
+      </c>
+      <c r="C74" s="10">
+        <v>4019291914922.1499</v>
+      </c>
+      <c r="D74" s="6">
+        <v>49175398817371</v>
+      </c>
+      <c r="E74" s="6">
+        <v>25970261367632.301</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B75" s="9">
+        <v>7.5083220399734696E-2</v>
+      </c>
+      <c r="C75" s="10">
+        <v>3753379301779.9102</v>
+      </c>
+      <c r="D75" s="6">
+        <v>49577418191926.203</v>
+      </c>
+      <c r="E75" s="6">
+        <v>23835806061624</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="1">
+        <v>43891</v>
+      </c>
+      <c r="B76" s="9">
+        <v>8.58992804234852E-2</v>
+      </c>
+      <c r="C76" s="10">
+        <v>4362252634654.6099</v>
+      </c>
+      <c r="D76" s="6">
+        <v>50162772742299.703</v>
+      </c>
+      <c r="E76" s="6">
+        <v>24402392648809.898</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="1">
+        <v>43922</v>
+      </c>
+      <c r="B77" s="9">
+        <v>8.1812959146415704E-2</v>
+      </c>
+      <c r="C77" s="10">
+        <v>4274899742072.8599</v>
+      </c>
+      <c r="D77" s="6">
+        <v>51812961343357</v>
+      </c>
+      <c r="E77" s="6">
+        <v>24608360826248.699</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="1">
+        <v>43952</v>
+      </c>
+      <c r="B78" s="9">
+        <v>8.2879711956215005E-2</v>
+      </c>
+      <c r="C78" s="10">
+        <v>4383202212441.9199</v>
+      </c>
+      <c r="D78" s="6">
+        <v>52380632230405</v>
+      </c>
+      <c r="E78" s="6">
+        <v>24920848219052.398</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="1">
+        <v>43983</v>
+      </c>
+      <c r="B79" s="9">
+        <v>9.3483672618282401E-2</v>
+      </c>
+      <c r="C79" s="10">
+        <v>4977574313854.0195</v>
+      </c>
+      <c r="D79" s="6">
+        <v>52910851370285.602</v>
+      </c>
+      <c r="E79" s="6">
+        <v>25518425340797.898</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="1">
+        <v>44013</v>
+      </c>
+      <c r="B80" s="9">
+        <v>8.4457918854705896E-2</v>
+      </c>
+      <c r="C80" s="10">
+        <v>4508479036264.3096</v>
+      </c>
+      <c r="D80" s="6">
+        <v>53339862198957.898</v>
+      </c>
+      <c r="E80" s="6">
+        <v>25766857368861.699</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="1">
+        <v>44044</v>
+      </c>
+      <c r="B81" s="9">
+        <v>8.0488645813055495E-2</v>
+      </c>
+      <c r="C81" s="10">
+        <v>4467444660248.3398</v>
+      </c>
+      <c r="D81" s="6">
+        <v>55375084847284.602</v>
+      </c>
+      <c r="E81" s="6">
+        <v>25871688713467.199</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="1">
+        <v>44075</v>
+      </c>
+      <c r="B82" s="9">
+        <v>8.0676790679165E-2</v>
+      </c>
+      <c r="C82" s="10">
+        <v>4505606239304.3701</v>
+      </c>
+      <c r="D82" s="6">
+        <v>55930124435138.898</v>
+      </c>
+      <c r="E82" s="6">
+        <v>26142931096027.199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="1">
+        <v>44105</v>
+      </c>
+      <c r="B83" s="9">
+        <v>8.5713562725451095E-2</v>
+      </c>
+      <c r="C83" s="10">
+        <v>4801474637883.9102</v>
+      </c>
+      <c r="D83" s="6">
+        <v>56380106845734.898</v>
+      </c>
+      <c r="E83" s="6">
+        <v>26420399431928</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="1">
+        <v>44136</v>
+      </c>
+      <c r="B84" s="9">
+        <v>8.9583985956087395E-2</v>
+      </c>
+      <c r="C84" s="10">
+        <v>5037519443542.9102</v>
+      </c>
+      <c r="D84" s="6">
+        <v>56906636963300.797</v>
+      </c>
+      <c r="E84" s="6">
+        <v>26734635726104.301</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="1">
+        <v>44166</v>
+      </c>
+      <c r="B85" s="9">
+        <v>7.7379423509926701E-2</v>
+      </c>
+      <c r="C85" s="10">
+        <v>4337375593636.4902</v>
+      </c>
+      <c r="D85" s="6">
+        <v>57272459188175.398</v>
+      </c>
+      <c r="E85" s="6">
+        <v>26806704354191.699</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="1">
+        <v>44197</v>
+      </c>
+      <c r="B86" s="9">
+        <v>8.6026543178650799E-2</v>
+      </c>
+      <c r="C86" s="10">
+        <v>4539206895370.75</v>
+      </c>
+      <c r="D86" s="6">
+        <v>52425360037096.297</v>
+      </c>
+      <c r="E86" s="6">
+        <v>27178294393512.699</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="1">
+        <v>44228</v>
+      </c>
+      <c r="B87" s="9">
+        <v>8.5053657854308198E-2</v>
+      </c>
+      <c r="C87" s="10">
+        <v>4536150826848.9199</v>
+      </c>
+      <c r="D87" s="6">
+        <v>52894882897886.898</v>
+      </c>
+      <c r="E87" s="6">
+        <v>27149462362277.602</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="1">
+        <v>44256</v>
+      </c>
+      <c r="B88" s="9">
+        <v>8.0097498054469904E-2</v>
+      </c>
+      <c r="C88" s="10">
+        <v>4302776227068.3501</v>
+      </c>
+      <c r="D88" s="6">
+        <v>53273357290003.297</v>
+      </c>
+      <c r="E88" s="6">
+        <v>27232165510555.301</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="1">
+        <v>44287</v>
+      </c>
+      <c r="B89" s="9">
+        <v>8.9463275102452305E-2</v>
+      </c>
+      <c r="C89" s="10">
+        <v>4855617693232.0195</v>
+      </c>
+      <c r="D89" s="6">
+        <v>53907576122425.5</v>
+      </c>
+      <c r="E89" s="6">
+        <v>27487710117628.301</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="1">
+        <v>44317</v>
+      </c>
+      <c r="B90" s="9">
+        <v>8.4376630189096899E-2</v>
+      </c>
+      <c r="C90" s="10">
+        <v>4614396682947.8701</v>
+      </c>
+      <c r="D90" s="6">
+        <v>54360249577527.398</v>
+      </c>
+      <c r="E90" s="6">
+        <v>27659263793668.102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B91" s="9">
+        <v>8.0220779866234201E-2</v>
+      </c>
+      <c r="C91" s="10">
+        <v>4412936442221.5596</v>
+      </c>
+      <c r="D91" s="6">
+        <v>54768197225495.898</v>
+      </c>
+      <c r="E91" s="6">
+        <v>27594598706028.699</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="1">
+        <v>44378</v>
+      </c>
+      <c r="B92" s="9">
+        <v>8.8422439121743204E-2</v>
+      </c>
+      <c r="C92" s="10">
+        <v>4987002515841.4102</v>
+      </c>
+      <c r="D92" s="6">
+        <v>56658515469299.797</v>
+      </c>
+      <c r="E92" s="6">
+        <v>27742966293907.398</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="1">
+        <v>44409</v>
+      </c>
+      <c r="B93" s="9">
+        <v>0.104035577676185</v>
+      </c>
+      <c r="C93" s="10">
+        <v>5958977376567.9102</v>
+      </c>
+      <c r="D93" s="6">
+        <v>57390329980984.898</v>
+      </c>
+      <c r="E93" s="6">
+        <v>28219108532224.398</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="1">
+        <v>44440</v>
+      </c>
+      <c r="B94" s="9">
+        <v>8.3461369075938902E-2</v>
+      </c>
+      <c r="C94" s="10">
+        <v>4805610072251.8896</v>
+      </c>
+      <c r="D94" s="6">
+        <v>57786318343893.5</v>
+      </c>
+      <c r="E94" s="6">
+        <v>28279617736164.199</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="1">
+        <v>44470</v>
+      </c>
+      <c r="B95" s="9">
+        <v>8.4512024969777805E-2</v>
+      </c>
+      <c r="C95" s="10">
+        <v>5029169194949.5498</v>
+      </c>
+      <c r="D95" s="6">
+        <v>59816388503659.898</v>
+      </c>
+      <c r="E95" s="6">
+        <v>28431929823186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="1">
+        <v>44501</v>
+      </c>
+      <c r="B96" s="9">
+        <v>8.0321219619475304E-2</v>
+      </c>
+      <c r="C96" s="10">
+        <v>4796572523249.5098</v>
+      </c>
+      <c r="D96" s="6">
+        <v>60399200975177.898</v>
+      </c>
+      <c r="E96" s="6">
+        <v>28527875976198</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="1">
+        <v>44531</v>
+      </c>
+      <c r="B97" s="9">
+        <v>8.5514053889586106E-2</v>
+      </c>
+      <c r="C97" s="10">
+        <v>5156670527211.4805</v>
+      </c>
+      <c r="D97" s="6">
+        <v>61087429215514.5</v>
+      </c>
+      <c r="E97" s="6">
+        <v>28749183377311.102</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="1">
+        <v>44562</v>
+      </c>
+      <c r="B98" s="9">
+        <v>8.2978336859101998E-2</v>
+      </c>
+      <c r="C98" s="10">
+        <v>4849866190681.8096</v>
+      </c>
+      <c r="D98" s="6">
+        <v>57846200499898.398</v>
+      </c>
+      <c r="E98" s="6">
+        <v>28698121387321.199</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="1">
+        <v>44593</v>
+      </c>
+      <c r="B99" s="9">
+        <v>8.2612966407060201E-2</v>
+      </c>
+      <c r="C99" s="10">
+        <v>4877654857688.8799</v>
+      </c>
+      <c r="D99" s="6">
+        <v>58375671229050.203</v>
+      </c>
+      <c r="E99" s="6">
+        <v>28655634508745</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="1">
+        <v>44621</v>
+      </c>
+      <c r="B100" s="9">
+        <v>9.2040236759519903E-2</v>
+      </c>
+      <c r="C100" s="10">
+        <v>5470162090523.5703</v>
+      </c>
+      <c r="D100" s="6">
+        <v>58843096014571</v>
+      </c>
+      <c r="E100" s="6">
+        <v>31224767160368.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="1">
+        <v>44652</v>
+      </c>
+      <c r="B101" s="9">
+        <v>9.5717233325832193E-2</v>
+      </c>
+      <c r="C101" s="10">
+        <v>5803162482693.5596</v>
+      </c>
+      <c r="D101" s="6">
+        <v>60238313968573.602</v>
+      </c>
+      <c r="E101" s="6">
+        <v>31766458312834.301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="1">
+        <v>44682</v>
+      </c>
+      <c r="B102" s="9">
+        <v>8.40673195599273E-2</v>
+      </c>
+      <c r="C102" s="10">
+        <v>5193174639787.8301</v>
+      </c>
+      <c r="D102" s="6">
+        <v>61643955135207</v>
+      </c>
+      <c r="E102" s="6">
+        <v>31798640024019.699</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="1">
+        <v>44713</v>
+      </c>
+      <c r="B103" s="9">
+        <v>8.7065646821639697E-2</v>
+      </c>
+      <c r="C103" s="10">
+        <v>5451549693853.4297</v>
+      </c>
+      <c r="D103" s="6">
+        <v>62330156591320.102</v>
+      </c>
+      <c r="E103" s="6">
+        <v>32188113271745.898</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B104" s="9">
+        <v>9.5044926704851498E-2</v>
+      </c>
+      <c r="C104" s="10">
+        <v>6124137033114.0596</v>
+      </c>
+      <c r="D104" s="6">
+        <v>64822573968722.898</v>
+      </c>
+      <c r="E104" s="6">
+        <v>32626280821381.102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="1">
+        <v>44774</v>
+      </c>
+      <c r="B105" s="9">
+        <v>8.5115337816090694E-2</v>
+      </c>
+      <c r="C105" s="10">
+        <v>5511885393844.1201</v>
+      </c>
+      <c r="D105" s="6">
+        <v>65320777626658.797</v>
+      </c>
+      <c r="E105" s="6">
+        <v>32746914836724.699</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="1">
+        <v>44805</v>
+      </c>
+      <c r="B106" s="9">
+        <v>8.7378968833408996E-2</v>
+      </c>
+      <c r="C106" s="10">
+        <v>5735292271125.0703</v>
+      </c>
+      <c r="D106" s="6">
+        <v>65987203293784.203</v>
+      </c>
+      <c r="E106" s="6">
+        <v>33117428345973.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="1">
+        <v>44835</v>
+      </c>
+      <c r="B107" s="9">
+        <v>8.6743171212498305E-2</v>
+      </c>
+      <c r="C107" s="10">
+        <v>5760958679166.0898</v>
+      </c>
+      <c r="D107" s="6">
+        <v>66755859907665.602</v>
+      </c>
+      <c r="E107" s="6">
+        <v>33414042168317.301</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="1">
+        <v>44866</v>
+      </c>
+      <c r="B108" s="9">
+        <v>8.6507631928772102E-2</v>
+      </c>
+      <c r="C108" s="10">
+        <v>5840692895829.4297</v>
+      </c>
+      <c r="D108" s="6">
+        <v>68273663120188.797</v>
+      </c>
+      <c r="E108" s="6">
+        <v>33731920500849.398</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="1">
+        <v>44896</v>
+      </c>
+      <c r="B109" s="9">
+        <v>9.64104536681816E-2</v>
+      </c>
+      <c r="C109" s="10">
+        <v>6895603875609.5898</v>
+      </c>
+      <c r="D109" s="6">
+        <v>72059133770069.906</v>
+      </c>
+      <c r="E109" s="6">
+        <v>34267282510084.699</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="1">
+        <v>44927</v>
+      </c>
+      <c r="B110" s="9">
+        <v>9.2471279405915999E-2</v>
+      </c>
+      <c r="C110" s="10">
+        <v>6399483481327.5</v>
+      </c>
+      <c r="D110" s="6">
+        <v>68535000985405.602</v>
+      </c>
+      <c r="E110" s="6">
+        <v>38409144059862.398</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B111" s="9">
+        <v>8.7646054564928605E-2</v>
+      </c>
+      <c r="C111" s="10">
+        <v>6140470203318.4297</v>
+      </c>
+      <c r="D111" s="6">
+        <v>69226113390794.102</v>
+      </c>
+      <c r="E111" s="6">
+        <v>35162597310269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="1">
+        <v>44986</v>
+      </c>
+      <c r="B112" s="9">
+        <v>7.8807918960605294E-2</v>
+      </c>
+      <c r="C112" s="10">
+        <v>5590541210762.8301</v>
+      </c>
+      <c r="D112" s="6">
+        <v>69988087351410.203</v>
+      </c>
+      <c r="E112" s="6">
+        <v>35460196472468.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="1">
+        <v>45017</v>
+      </c>
+      <c r="B113" s="9">
+        <v>8.4964481733083894E-2</v>
+      </c>
+      <c r="C113" s="10">
+        <v>6029010056283.1104</v>
+      </c>
+      <c r="D113" s="6">
+        <v>70485602564559.203</v>
+      </c>
+      <c r="E113" s="6">
+        <v>35434648252190.203</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="1">
+        <v>45047</v>
+      </c>
+      <c r="B114" s="9">
+        <v>9.04035060797512E-2</v>
+      </c>
+      <c r="C114" s="10">
+        <v>6437539783254.1396</v>
+      </c>
+      <c r="D114" s="6">
+        <v>71180650486938.297</v>
+      </c>
+      <c r="E114" s="6">
+        <v>36067915906594.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="1">
+        <v>45078</v>
+      </c>
+      <c r="B115" s="9">
+        <v>8.1232046453651702E-2</v>
+      </c>
+      <c r="C115" s="10">
+        <v>5863892409962.2002</v>
+      </c>
+      <c r="D115" s="6">
+        <v>71878053121680.797</v>
+      </c>
+      <c r="E115" s="6">
+        <v>36333473668503.203</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="1">
+        <v>45108</v>
+      </c>
+      <c r="B116" s="9">
+        <v>8.2680230139998395E-2</v>
+      </c>
+      <c r="C116" s="10">
+        <v>5953251764265.1201</v>
+      </c>
+      <c r="D116" s="6">
+        <v>72384501492022.906</v>
+      </c>
+      <c r="E116" s="6">
+        <v>36526613321272.297</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="1">
+        <v>45139</v>
+      </c>
+      <c r="B117" s="9">
+        <v>8.1372366208738098E-2</v>
+      </c>
+      <c r="C117" s="10">
+        <v>5880377750242.0596</v>
+      </c>
+      <c r="D117" s="6">
+        <v>73030885631114.703</v>
+      </c>
+      <c r="E117" s="6">
+        <v>36948076780272.398</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="1">
+        <v>45170</v>
+      </c>
+      <c r="B118" s="9">
+        <v>8.8901994004083801E-2</v>
+      </c>
+      <c r="C118" s="10">
+        <v>6538988522600.9502</v>
+      </c>
+      <c r="D118" s="6">
+        <v>73800877421722.406</v>
+      </c>
+      <c r="E118" s="6">
+        <v>37343584662182.398</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="1">
+        <v>45200</v>
+      </c>
+      <c r="B119" s="9">
+        <v>8.3845193559471301E-2</v>
+      </c>
+      <c r="C119" s="10">
+        <v>6314978708892.3896</v>
+      </c>
+      <c r="D119" s="6">
+        <v>75891785584749.703</v>
+      </c>
+      <c r="E119" s="6">
+        <v>37689568555458.703</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="1">
+        <v>45231</v>
+      </c>
+      <c r="B120" s="9">
+        <v>8.5073186550348096E-2</v>
+      </c>
+      <c r="C120" s="10">
+        <v>6444446842620.6299</v>
+      </c>
+      <c r="D120" s="6">
+        <v>76635093039934.797</v>
+      </c>
+      <c r="E120" s="6">
+        <v>38165731665117.203</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="1">
+        <v>45261</v>
+      </c>
+      <c r="B121" s="9">
+        <v>9.1952130275764807E-2</v>
+      </c>
+      <c r="C121" s="10">
+        <v>7079486932784.6602</v>
+      </c>
+      <c r="D121" s="6">
+        <v>77317525732596.906</v>
+      </c>
+      <c r="E121" s="6">
+        <v>38480304481737.898</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="1">
+        <v>45292</v>
+      </c>
+      <c r="B122" s="9">
+        <v>7.5127429417866695E-2</v>
+      </c>
+      <c r="C122" s="10">
+        <v>6211721972359.4502</v>
+      </c>
+      <c r="D122" s="6">
+        <v>81944243928242.906</v>
+      </c>
+      <c r="E122" s="6">
+        <v>38775331131404.398</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="1">
+        <v>45323</v>
+      </c>
+      <c r="B123" s="9">
+        <v>8.9619935322301697E-2</v>
+      </c>
+      <c r="C123" s="10">
+        <v>7484235732454.0596</v>
+      </c>
+      <c r="D123" s="6">
+        <v>82606426885707.797</v>
+      </c>
+      <c r="E123" s="6">
+        <v>39598200408417.602</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="1">
+        <v>45352</v>
+      </c>
+      <c r="B124" s="9">
+        <v>8.0766249702229995E-2</v>
+      </c>
+      <c r="C124" s="10">
+        <v>6831633397381.4697</v>
+      </c>
+      <c r="D124" s="6">
+        <v>83473845167388.594</v>
+      </c>
+      <c r="E124" s="6">
+        <v>40219631318581.203</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="1">
+        <v>45383</v>
+      </c>
+      <c r="B125" s="9">
+        <v>8.0625930584049404E-2</v>
+      </c>
+      <c r="C125" s="10">
+        <v>6804763976850.75</v>
+      </c>
+      <c r="D125" s="6">
+        <v>84119553770892.594</v>
+      </c>
+      <c r="E125" s="6">
+        <v>40712263524997</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="1">
+        <v>45413</v>
+      </c>
+      <c r="B126" s="9">
+        <v>8.5050356519002598E-2</v>
+      </c>
+      <c r="C126" s="10">
+        <v>7208413656498</v>
+      </c>
+      <c r="D126" s="6">
+        <v>84826059823558.703</v>
+      </c>
+      <c r="E126" s="6">
+        <v>41366968674241.102</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="1">
+        <v>45444</v>
+      </c>
+      <c r="B127" s="9">
+        <v>8.4539226494870306E-2</v>
+      </c>
+      <c r="C127" s="10">
+        <v>7257282263627.6299</v>
+      </c>
+      <c r="D127" s="6">
+        <v>85465161517855.5</v>
+      </c>
+      <c r="E127" s="6">
+        <v>41960552221665.297</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="1">
+        <v>45474</v>
+      </c>
+      <c r="B128" s="9">
+        <v>7.9371942482406296E-2</v>
+      </c>
+      <c r="C128" s="10">
+        <v>6826726918815.7998</v>
+      </c>
+      <c r="D128" s="6">
+        <v>86331578899637.5</v>
+      </c>
+      <c r="E128" s="6">
+        <v>42484760543668.898</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="1">
+        <v>45505</v>
+      </c>
+      <c r="B129" s="9">
+        <v>7.8114052472375003E-2</v>
+      </c>
+      <c r="C129" s="10">
+        <v>6759561593921.4297</v>
+      </c>
+      <c r="D129" s="6">
+        <v>87071717504314.703</v>
+      </c>
+      <c r="E129" s="6">
+        <v>43051305259321.898</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="1">
+        <v>45536</v>
+      </c>
+      <c r="B130" s="9">
+        <v>8.7896950315989805E-2</v>
+      </c>
+      <c r="C130" s="10">
+        <v>7708953737149.0195</v>
+      </c>
+      <c r="D130" s="6">
+        <v>87895491479406.297</v>
+      </c>
+      <c r="E130" s="6">
+        <v>43743381988165.297</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="1">
+        <v>45566</v>
+      </c>
+      <c r="B131" s="9">
+        <v>9.0483862548421196E-2</v>
+      </c>
+      <c r="C131" s="10">
+        <v>7935914085121.6797</v>
+      </c>
+      <c r="D131" s="6">
+        <v>88493095553448.297</v>
+      </c>
+      <c r="E131" s="6">
+        <v>44496205677132.102</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="1">
+        <v>45597</v>
+      </c>
+      <c r="B132" s="9">
+        <v>8.7245649684903198E-2</v>
+      </c>
+      <c r="C132" s="10">
+        <v>7817943657621.54</v>
+      </c>
+      <c r="D132" s="6">
+        <v>90641430596447.203</v>
+      </c>
+      <c r="E132" s="6">
+        <v>45039220590106.898</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="1">
+        <v>45627</v>
+      </c>
+      <c r="B133" s="9">
+        <v>9.2754257365083401E-2</v>
+      </c>
+      <c r="C133" s="10">
+        <v>8446434341510.0703</v>
+      </c>
+      <c r="D133" s="6">
+        <v>91427525010427.5</v>
+      </c>
+      <c r="E133" s="6">
+        <v>46055747311949.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="1">
+        <v>45658</v>
+      </c>
+      <c r="B134" s="9">
+        <v>9.4648840148752106E-2</v>
+      </c>
+      <c r="C134" s="10">
+        <v>8803337086709.9805</v>
+      </c>
+      <c r="D134" s="6">
+        <v>92117981650437.203</v>
+      </c>
+      <c r="E134" s="6">
+        <v>53670489712636.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="1">
+        <v>45689</v>
+      </c>
+      <c r="B135" s="9">
+        <v>8.9274952186445003E-2</v>
+      </c>
+      <c r="C135" s="10">
+        <v>8386429039459.7803</v>
+      </c>
+      <c r="D135" s="6">
+        <v>92906054185175.406</v>
+      </c>
+      <c r="E135" s="6">
+        <v>47026030091285.398</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="1">
+        <v>45717</v>
+      </c>
+      <c r="B136" s="9">
+        <v>8.2178459924033595E-2</v>
+      </c>
+      <c r="C136" s="10">
+        <v>7746238989239.2305</v>
+      </c>
+      <c r="D136" s="6">
+        <v>93473775572342.094</v>
+      </c>
+      <c r="E136" s="6">
+        <v>47421829804938.203</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B137" s="9">
+        <v>8.7383638646355802E-2</v>
+      </c>
+      <c r="C137" s="10">
+        <v>8264018783506.4502</v>
+      </c>
+      <c r="D137" s="6">
+        <v>94361591637368.297</v>
+      </c>
+      <c r="E137" s="6">
+        <v>48132518637623.102</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B138" s="9">
+        <v>8.1859991349919198E-2</v>
+      </c>
+      <c r="C138" s="10">
+        <v>7786723613647.7803</v>
+      </c>
+      <c r="D138" s="6">
+        <v>95125262125412.906</v>
+      </c>
+      <c r="E138" s="6">
+        <v>48490388398703.398</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B139" s="9">
+        <v>8.4499909760430703E-2</v>
+      </c>
+      <c r="C139" s="10">
+        <v>8139649009833.6602</v>
+      </c>
+      <c r="D139" s="6">
+        <v>95920826292208.094</v>
+      </c>
+      <c r="E139" s="6">
+        <v>49037213548821.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B140" s="9">
+        <v>8.9970028400459798E-2</v>
+      </c>
+      <c r="C140" s="10">
+        <v>8701374024078.4805</v>
+      </c>
+      <c r="D140" s="6">
+        <v>96718675747331.094</v>
+      </c>
+      <c r="E140" s="6">
+        <v>49710472697832.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B141" s="9">
+        <v>8.1902054125262899E-2</v>
+      </c>
+      <c r="C141" s="10">
+        <v>7962624933495.4102</v>
+      </c>
+      <c r="D141" s="6">
+        <v>97470440058302.297</v>
+      </c>
+      <c r="E141" s="6">
+        <v>50225979102317.703</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B142" s="9">
+        <v>7.8544620634035306E-2</v>
+      </c>
+      <c r="C142" s="10">
+        <v>7665434970036.4502</v>
+      </c>
+      <c r="D142" s="6">
+        <v>98087751496131.203</v>
+      </c>
+      <c r="E142" s="6">
+        <v>50662815044691.297</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B143" s="9">
+        <v>8.3363081531965103E-2</v>
+      </c>
+      <c r="C143" s="10">
+        <v>8175228894320.5498</v>
+      </c>
+      <c r="D143" s="6">
+        <v>98981151670748.906</v>
+      </c>
+      <c r="E143" s="6">
+        <v>51135083400815.297</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B144" s="9">
+        <v>8.4909452778031094E-2</v>
+      </c>
+      <c r="C144" s="10">
+        <v>8360999002487.3398</v>
+      </c>
+      <c r="D144" s="6">
+        <v>99697199732015.906</v>
+      </c>
+      <c r="E144" s="6">
+        <v>51718975118447.602</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B145" s="9">
+        <v>7.1722848855008098E-2</v>
+      </c>
+      <c r="C145" s="10">
+        <v>7039749594656.1201</v>
+      </c>
+      <c r="D145" s="6">
+        <v>98718029709985.406</v>
+      </c>
+      <c r="E145" s="6">
+        <v>51789818095407.797</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A146" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B146" s="9">
+        <v>8.8611890065537394E-2</v>
+      </c>
+      <c r="C146" s="10">
+        <v>8915922239360.0605</v>
+      </c>
+      <c r="D146" s="6">
+        <v>99541518114128.906</v>
+      </c>
+      <c r="E146" s="6">
+        <v>52880307057857.703</v>
       </c>
     </row>
   </sheetData>
